--- a/api/clv1/codelist/UNSDG-Indicators.xlsx
+++ b/api/clv1/codelist/UNSDG-Indicators.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="823">
   <si>
     <t>code</t>
   </si>
@@ -130,22 +130,34 @@
     <t>Proportion of local governments that adopt and implement local disaster risk reduction strategies in line with national disaster risk reduction strategies</t>
   </si>
   <si>
+    <t>1.a.1</t>
+  </si>
+  <si>
+    <t>Total official development assistance grants from all donors that focus on poverty reduction as a share of the recipient country’s gross national income</t>
+  </si>
+  <si>
+    <t>1.a</t>
+  </si>
+  <si>
+    <t>Ensure significant mobilization of resources from a variety of sources, including through enhanced development cooperation, in order to provide adequate and predictable means for developing countries, in particular least developed countries, to implement programmes and policies to end poverty in all its dimensions</t>
+  </si>
+  <si>
     <t>1.a.2</t>
   </si>
   <si>
     <t>Proportion of total government spending on essential services (education, health and social protection)</t>
   </si>
   <si>
-    <t>1.a</t>
-  </si>
-  <si>
-    <t>Ensure significant mobilization of resources from a variety of sources, including through enhanced development cooperation, in order to provide adequate and predictable means for developing countries, in particular least developed countries, to implement programmes and policies to end poverty in all its dimensions</t>
-  </si>
-  <si>
-    <t>1.a.1</t>
-  </si>
-  <si>
-    <t>Total official development assistance grants from all donors that focus on poverty reduction as a share of the recipient country’s gross national income</t>
+    <t>1.b.1</t>
+  </si>
+  <si>
+    <t>Pro-poor public social spending</t>
+  </si>
+  <si>
+    <t>1.b</t>
+  </si>
+  <si>
+    <t>Create sound policy frameworks at the national, regional and international levels, based on pro-poor and gender-sensitive development strategies, to support accelerated investment in poverty eradication actions</t>
   </si>
   <si>
     <t>2.1.1</t>
@@ -208,6 +220,18 @@
     <t>Average income of small-scale food producers, by sex and indigenous status</t>
   </si>
   <si>
+    <t>2.4.1</t>
+  </si>
+  <si>
+    <t>Proportion of agricultural area under productive and sustainable agriculture</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>By 2030, ensure sustainable food production systems and implement resilient agricultural practices that increase productivity and production, that help maintain ecosystems, that strengthen capacity for adaptation to climate change, extreme weather, drought, flooding and other disasters and that progressively improve land and soil quality</t>
+  </si>
+  <si>
     <t>2.5.1</t>
   </si>
   <si>
@@ -328,18 +352,18 @@
     <t>Malaria incidence per 1,000 population</t>
   </si>
   <si>
+    <t>3.3.4</t>
+  </si>
+  <si>
+    <t>Hepatitis B incidence per 100,000 population</t>
+  </si>
+  <si>
     <t>3.3.5</t>
   </si>
   <si>
     <t>Number of people requiring interventions against neglected tropical diseases</t>
   </si>
   <si>
-    <t>3.3.4</t>
-  </si>
-  <si>
-    <t>Hepatitis B incidence per 100,000 population</t>
-  </si>
-  <si>
     <t>3.4.1</t>
   </si>
   <si>
@@ -358,24 +382,24 @@
     <t>Suicide mortality rate</t>
   </si>
   <si>
+    <t>3.5.1</t>
+  </si>
+  <si>
+    <t>Coverage of treatment interventions (pharmacological, psychosocial and rehabilitation and aftercare services) for substance use disorders</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>Strengthen the prevention and treatment of substance abuse, including narcotic drug abuse and harmful use of alcohol</t>
+  </si>
+  <si>
     <t>3.5.2</t>
   </si>
   <si>
     <t>Alcohol per capita consumption (aged 15 years and older) within a calendar year in litres of pure alcohol</t>
   </si>
   <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>Strengthen the prevention and treatment of substance abuse, including narcotic drug abuse and harmful use of alcohol</t>
-  </si>
-  <si>
-    <t>3.5.1</t>
-  </si>
-  <si>
-    <t>Coverage of treatment interventions (pharmacological, psychosocial and rehabilitation and aftercare services) for substance use disorders</t>
-  </si>
-  <si>
     <t>3.6.1</t>
   </si>
   <si>
@@ -406,24 +430,24 @@
     <t>Adolescent birth rate (aged 10-14 years; aged 15-19 years) per 1,000 women in that age group</t>
   </si>
   <si>
+    <t>3.8.1</t>
+  </si>
+  <si>
+    <t>Coverage of essential health services</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>Achieve universal health coverage, including financial risk protection, access to quality essential health-care services and access to safe, effective, quality and affordable essential medicines and vaccines for all</t>
+  </si>
+  <si>
     <t>3.8.2</t>
   </si>
   <si>
     <t>Proportion of population with large household expenditures on health as a share of total household expenditure or income</t>
   </si>
   <si>
-    <t>3.8</t>
-  </si>
-  <si>
-    <t>Achieve universal health coverage, including financial risk protection, access to quality essential health-care services and access to safe, effective, quality and affordable essential medicines and vaccines for all</t>
-  </si>
-  <si>
-    <t>3.8.1</t>
-  </si>
-  <si>
-    <t>Coverage of essential health services</t>
-  </si>
-  <si>
     <t>3.9.1</t>
   </si>
   <si>
@@ -460,24 +484,24 @@
     <t>Strengthen the implementation of the World Health Organization Framework Convention on Tobacco Control in all countries, as appropriate</t>
   </si>
   <si>
+    <t>3.b.1</t>
+  </si>
+  <si>
+    <t>Proportion of the target population covered by all vaccines included in their national programme</t>
+  </si>
+  <si>
+    <t>3.b</t>
+  </si>
+  <si>
+    <t>Support the research and development of vaccines and medicines for the communicable and non‑communicable diseases that primarily affect developing countries, provide access to affordable essential medicines and vaccines, in accordance with the Doha Declaration on the TRIPS Agreement and Public Health, which affirms the right of developing countries to use to the full the provisions in the Agreement on Trade-Related Aspects of Intellectual Property Rights regarding flexibilities to protect public health, and, in particular, provide access to medicines for all</t>
+  </si>
+  <si>
     <t>3.b.2</t>
   </si>
   <si>
     <t>Total net official development assistance to medical research and basic health sectors</t>
   </si>
   <si>
-    <t>3.b</t>
-  </si>
-  <si>
-    <t>Support the research and development of vaccines and medicines for the communicable and non‑communicable diseases that primarily affect developing countries, provide access to affordable essential medicines and vaccines, in accordance with the Doha Declaration on the TRIPS Agreement and Public Health, which affirms the right of developing countries to use to the full the provisions in the Agreement on Trade-Related Aspects of Intellectual Property Rights regarding flexibilities to protect public health, and, in particular, provide access to medicines for all</t>
-  </si>
-  <si>
-    <t>3.b.1</t>
-  </si>
-  <si>
-    <t>Proportion of the target population covered by all vaccines included in their national programme</t>
-  </si>
-  <si>
     <t>3.b.3</t>
   </si>
   <si>
@@ -598,6 +622,18 @@
     <t>By 2030, ensure that all youth and a substantial proportion of adults, both men and women, achieve literacy and numeracy</t>
   </si>
   <si>
+    <t>4.7.1</t>
+  </si>
+  <si>
+    <t>Extent to which (i) global citizenship education and (ii) education for sustainable development are mainstreamed in (a) national education policies; (b) curricula; (c) teacher education; and (d) student assessment</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>By 2030, ensure that all learners acquire the knowledge and skills needed to promote sustainable development, including, among others, through education for sustainable development and sustainable lifestyles, human rights, gender equality, promotion of a culture of peace and non-violence, global citizenship and appreciation of cultural diversity and of culture’s contribution to sustainable development</t>
+  </si>
+  <si>
     <t>4.a.1</t>
   </si>
   <si>
@@ -658,6 +694,12 @@
     <t>Eliminate all forms of violence against all women and girls in the public and private spheres, including trafficking and sexual and other types of exploitation</t>
   </si>
   <si>
+    <t>5.2.2</t>
+  </si>
+  <si>
+    <t>Proportion of women and girls aged 15 years and older subjected to sexual violence by persons other than an intimate partner in the previous 12 months, by age and place of occurrence</t>
+  </si>
+  <si>
     <t>5.3.1</t>
   </si>
   <si>
@@ -790,22 +832,34 @@
     <t>By 2030, achieve access to adequate and equitable sanitation and hygiene for all and end open defecation, paying special attention to the needs of women and girls and those in vulnerable situations</t>
   </si>
   <si>
+    <t>6.3.1</t>
+  </si>
+  <si>
+    <t>Proportion of domestic and industrial wastewater flows safely treated</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>By 2030, improve water quality by reducing pollution, eliminating dumping and minimizing release of hazardous chemicals and materials, halving the proportion of untreated wastewater and substantially increasing recycling and safe reuse globally</t>
+  </si>
+  <si>
     <t>6.3.2</t>
   </si>
   <si>
     <t>Proportion of bodies of water with good ambient water quality</t>
   </si>
   <si>
-    <t>6.3</t>
-  </si>
-  <si>
-    <t>By 2030, improve water quality by reducing pollution, eliminating dumping and minimizing release of hazardous chemicals and materials, halving the proportion of untreated wastewater and substantially increasing recycling and safe reuse globally</t>
-  </si>
-  <si>
-    <t>6.3.1</t>
-  </si>
-  <si>
-    <t>Proportion of domestic and industrial wastewater flows safely treated</t>
+    <t>6.4.1</t>
+  </si>
+  <si>
+    <t>Change in water-use efficiency over time</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>By 2030, substantially increase water-use efficiency across all sectors and ensure sustainable withdrawals and supply of freshwater to address water scarcity and substantially reduce the number of people suffering from water scarcity</t>
   </si>
   <si>
     <t>6.4.2</t>
@@ -814,18 +868,6 @@
     <t>Level of water stress: freshwater withdrawal as a proportion of available freshwater resources</t>
   </si>
   <si>
-    <t>6.4</t>
-  </si>
-  <si>
-    <t>By 2030, substantially increase water-use efficiency across all sectors and ensure sustainable withdrawals and supply of freshwater to address water scarcity and substantially reduce the number of people suffering from water scarcity</t>
-  </si>
-  <si>
-    <t>6.4.1</t>
-  </si>
-  <si>
-    <t>Change in water-use efficiency over time</t>
-  </si>
-  <si>
     <t>6.5.1</t>
   </si>
   <si>
@@ -946,6 +988,18 @@
     <t>By 2030, expand infrastructure and upgrade technology for supplying modern and sustainable energy services for all in developing countries, in particular least developed countries, small island developing States and landlocked developing countries, in accordance with their respective programmes of support</t>
   </si>
   <si>
+    <t>8.1.1</t>
+  </si>
+  <si>
+    <t>Annual growth rate of real GDP per capita</t>
+  </si>
+  <si>
+    <t>8.1</t>
+  </si>
+  <si>
+    <t>Sustain per capita economic growth in accordance with national circumstances and, in particular, at least 7 per cent gross domestic product growth per annum in the least developed countries</t>
+  </si>
+  <si>
     <t>8.2.1</t>
   </si>
   <si>
@@ -1030,18 +1084,6 @@
     <t xml:space="preserve">Take immediate and effective measures to eradicate forced labour, end modern slavery and human trafficking and secure the prohibition and elimination of the worst forms of child labour, including recruitment and use of child soldiers, and by 2025 end child labour in all its forms </t>
   </si>
   <si>
-    <t>8.1.1</t>
-  </si>
-  <si>
-    <t>Annual growth rate of real GDP per capita</t>
-  </si>
-  <si>
-    <t>8.1</t>
-  </si>
-  <si>
-    <t>Sustain per capita economic growth in accordance with national circumstances and, in particular, at least 7 per cent gross domestic product growth per annum in the least developed countries</t>
-  </si>
-  <si>
     <t>8.8.1</t>
   </si>
   <si>
@@ -1114,24 +1156,24 @@
     <t>By 2020, develop and operationalize a global strategy for youth employment and implement the Global Jobs Pact of the International Labour Organization</t>
   </si>
   <si>
+    <t>9.1.1</t>
+  </si>
+  <si>
+    <t>Proportion of the rural population who live within 2 km of an all-season road</t>
+  </si>
+  <si>
+    <t>9.1</t>
+  </si>
+  <si>
+    <t>Develop quality, reliable, sustainable and resilient infrastructure, including regional and transborder infrastructure, to support economic development and human well-being, with a focus on affordable and equitable access for all</t>
+  </si>
+  <si>
     <t>9.1.2</t>
   </si>
   <si>
     <t>Passenger and freight volumes, by mode of transport</t>
   </si>
   <si>
-    <t>9.1</t>
-  </si>
-  <si>
-    <t>Develop quality, reliable, sustainable and resilient infrastructure, including regional and transborder infrastructure, to support economic development and human well-being, with a focus on affordable and equitable access for all</t>
-  </si>
-  <si>
-    <t>9.1.1</t>
-  </si>
-  <si>
-    <t>Proportion of the rural population who live within 2 km of an all-season road</t>
-  </si>
-  <si>
     <t>9.2.1</t>
   </si>
   <si>
@@ -1312,18 +1354,24 @@
     <t>Ensure enhanced representation and voice for developing countries in decision-making in global international economic and financial institutions in order to deliver more effective, credible, accountable and legitimate institutions</t>
   </si>
   <si>
+    <t>10.7.1</t>
+  </si>
+  <si>
+    <t>Recruitment cost borne by employee as a proportion of monthly income earned in country of destination</t>
+  </si>
+  <si>
+    <t>10.7</t>
+  </si>
+  <si>
+    <t>Facilitate orderly, safe, regular and responsible migration and mobility of people, including through the implementation of planned and well-managed migration policies</t>
+  </si>
+  <si>
     <t>10.7.2</t>
   </si>
   <si>
     <t>Number of countries with migration policies that facilitate orderly, safe, regular and responsible migration and mobility of people</t>
   </si>
   <si>
-    <t>10.7</t>
-  </si>
-  <si>
-    <t>Facilitate orderly, safe, regular and responsible migration and mobility of people, including through the implementation of planned and well-managed migration policies</t>
-  </si>
-  <si>
     <t>10.7.3</t>
   </si>
   <si>
@@ -1384,6 +1432,48 @@
     <t>By 2030, ensure access for all to adequate, safe and affordable housing and basic services and upgrade slums</t>
   </si>
   <si>
+    <t>11.2.1</t>
+  </si>
+  <si>
+    <t>Proportion of population that has convenient access to public transport, by sex, age and persons with disabilities</t>
+  </si>
+  <si>
+    <t>11.2</t>
+  </si>
+  <si>
+    <t>By 2030, provide access to safe, affordable, accessible and sustainable transport systems for all, improving road safety, notably by expanding public transport, with special attention to the needs of those in vulnerable situations, women, children, persons with disabilities and older persons</t>
+  </si>
+  <si>
+    <t>11.3.1</t>
+  </si>
+  <si>
+    <t>Ratio of land consumption rate to population growth rate</t>
+  </si>
+  <si>
+    <t>11.3</t>
+  </si>
+  <si>
+    <t>By 2030, enhance inclusive and sustainable urbanization and capacity for participatory, integrated and sustainable human settlement planning and management in all countries</t>
+  </si>
+  <si>
+    <t>11.3.2</t>
+  </si>
+  <si>
+    <t>Proportion of cities with a direct participation structure of civil society in urban planning and management that operate regularly and democratically</t>
+  </si>
+  <si>
+    <t>11.4.1</t>
+  </si>
+  <si>
+    <t>Total per capita expenditure on the preservation, protection and conservation of all cultural and natural heritage, by source of funding (public, private), type of heritage (cultural, natural) and level of government (national, regional, and local/municipal)</t>
+  </si>
+  <si>
+    <t>11.4</t>
+  </si>
+  <si>
+    <t>Strengthen efforts to protect and safeguard the world’s cultural and natural heritage</t>
+  </si>
+  <si>
     <t>11.5.1</t>
   </si>
   <si>
@@ -1417,6 +1507,24 @@
     <t>Annual mean levels of fine particulate matter (e.g. PM2.5 and PM10) in cities (population weighted)</t>
   </si>
   <si>
+    <t>11.7.1</t>
+  </si>
+  <si>
+    <t>Average share of the built-up area of cities that is open space for public use for all, by sex, age and persons with disabilities</t>
+  </si>
+  <si>
+    <t>11.7</t>
+  </si>
+  <si>
+    <t>By 2030, provide universal access to safe, inclusive and accessible, green and public spaces, in particular for women and children, older persons and persons with disabilities</t>
+  </si>
+  <si>
+    <t>11.7.2</t>
+  </si>
+  <si>
+    <t>Proportion of persons victim of physical or sexual harassment, by sex, age, disability status and place of occurrence, in the previous 12 months</t>
+  </si>
+  <si>
     <t>11.a.1</t>
   </si>
   <si>
@@ -1531,6 +1639,15 @@
     <t>Promote public procurement practices that are sustainable, in accordance with national policies and priorities</t>
   </si>
   <si>
+    <t>12.8.1</t>
+  </si>
+  <si>
+    <t>12.8</t>
+  </si>
+  <si>
+    <t>By 2030, ensure that people everywhere have the relevant information and awareness for sustainable development and lifestyles in harmony with nature</t>
+  </si>
+  <si>
     <t>12.a.1</t>
   </si>
   <si>
@@ -1579,22 +1696,31 @@
     <t>13.1.3</t>
   </si>
   <si>
+    <t>13.2.1</t>
+  </si>
+  <si>
+    <t>Number of countries with nationally determined contributions, long-term strategies, national adaptation plans and adaptation communications, as reported to the secretariat of the United Nations Framework Convention on Climate Change</t>
+  </si>
+  <si>
+    <t>13.2</t>
+  </si>
+  <si>
+    <t>Integrate climate change measures into national policies, strategies and planning</t>
+  </si>
+  <si>
     <t>13.2.2</t>
   </si>
   <si>
     <t>Total greenhouse gas emissions per year</t>
   </si>
   <si>
-    <t>13.2</t>
-  </si>
-  <si>
-    <t>Integrate climate change measures into national policies, strategies and planning</t>
-  </si>
-  <si>
-    <t>13.2.1</t>
-  </si>
-  <si>
-    <t>Number of countries with nationally determined contributions, long-term strategies, national adaptation plans and adaptation communications, as reported to the secretariat of the United Nations Framework Convention on Climate Change</t>
+    <t>13.3.1</t>
+  </si>
+  <si>
+    <t>13.3</t>
+  </si>
+  <si>
+    <t>Improve education, awareness-raising and human and institutional capacity on climate change mitigation, adaptation, impact reduction and early warning</t>
   </si>
   <si>
     <t>13.a.1</t>
@@ -1633,6 +1759,54 @@
     <t>By 2025, prevent and significantly reduce marine pollution of all kinds, in particular from land-based activities, including marine debris and nutrient pollution</t>
   </si>
   <si>
+    <t>14.2.1</t>
+  </si>
+  <si>
+    <t>Number of countries using ecosystem-based approaches to managing marine areas</t>
+  </si>
+  <si>
+    <t>14.2</t>
+  </si>
+  <si>
+    <t>By 2020, sustainably manage and protect marine and coastal ecosystems to avoid significant adverse impacts, including by strengthening their resilience, and take action for their restoration in order to achieve healthy and productive oceans</t>
+  </si>
+  <si>
+    <t>14.3.1</t>
+  </si>
+  <si>
+    <t>Average marine acidity (pH) measured at agreed suite of representative sampling stations</t>
+  </si>
+  <si>
+    <t>14.3</t>
+  </si>
+  <si>
+    <t>Minimize and address the impacts of ocean acidification, including through enhanced scientific cooperation at all levels</t>
+  </si>
+  <si>
+    <t>14.4.1</t>
+  </si>
+  <si>
+    <t>Proportion of fish stocks within biologically sustainable levels</t>
+  </si>
+  <si>
+    <t>14.4</t>
+  </si>
+  <si>
+    <t>By 2020, effectively regulate harvesting and end overfishing, illegal, unreported and unregulated fishing and destructive fishing practices and implement science-based management plans, in order to restore fish stocks in the shortest time feasible, at least to levels that can produce maximum sustainable yield as determined by their biological characteristics</t>
+  </si>
+  <si>
+    <t>14.5.1</t>
+  </si>
+  <si>
+    <t>Coverage of protected areas in relation to marine areas</t>
+  </si>
+  <si>
+    <t>14.5</t>
+  </si>
+  <si>
+    <t>By 2020, conserve at least 10 per cent of coastal and marine areas, consistent with national and international law and based on the best available scientific information</t>
+  </si>
+  <si>
     <t>14.6.1</t>
   </si>
   <si>
@@ -1657,18 +1831,6 @@
     <t>By 2030, increase the economic benefits to small island developing States and least developed countries from the sustainable use of marine resources, including through sustainable management of fisheries, aquaculture and tourism</t>
   </si>
   <si>
-    <t>14.3.1</t>
-  </si>
-  <si>
-    <t>Average marine acidity (pH) measured at agreed suite of representative sampling stations</t>
-  </si>
-  <si>
-    <t>14.3</t>
-  </si>
-  <si>
-    <t>Minimize and address the impacts of ocean acidification, including through enhanced scientific cooperation at all levels</t>
-  </si>
-  <si>
     <t>14.a.1</t>
   </si>
   <si>
@@ -1681,22 +1843,10 @@
     <t>Increase scientific knowledge, develop research capacity and transfer marine technology, taking into account the Intergovernmental Oceanographic Commission Criteria and Guidelines on the Transfer of Marine Technology, in order to improve ocean health and to enhance the contribution of marine biodiversity to the development of developing countries, in particular small island developing States and least developed countries</t>
   </si>
   <si>
-    <t>14.4.1</t>
-  </si>
-  <si>
-    <t>Proportion of fish stocks within biologically sustainable levels</t>
-  </si>
-  <si>
-    <t>14.4</t>
-  </si>
-  <si>
-    <t>By 2020, effectively regulate harvesting and end overfishing, illegal, unreported and unregulated fishing and destructive fishing practices and implement science-based management plans, in order to restore fish stocks in the shortest time feasible, at least to levels that can produce maximum sustainable yield as determined by their biological characteristics</t>
-  </si>
-  <si>
     <t>14.b.1</t>
   </si>
   <si>
-    <t>Degree of application of a legal/regulatory/policy/institutional framework which recognizes and protects access rights for small-scale fisheries</t>
+    <t>Degree of application of a legal/regulatory/ policy/institutional framework which recognizes and protects access rights for small-scale fisheries</t>
   </si>
   <si>
     <t>14.b</t>
@@ -1705,18 +1855,6 @@
     <t>Provide access for small-scale artisanal fishers to marine resources and markets</t>
   </si>
   <si>
-    <t>14.5.1</t>
-  </si>
-  <si>
-    <t>Coverage of protected areas in relation to marine areas</t>
-  </si>
-  <si>
-    <t>14.5</t>
-  </si>
-  <si>
-    <t>By 2020, conserve at least 10 per cent of coastal and marine areas, consistent with national and international law and based on the best available scientific information</t>
-  </si>
-  <si>
     <t>14.c.1</t>
   </si>
   <si>
@@ -1813,6 +1951,18 @@
     <t>Promote fair and equitable sharing of the benefits arising from the utilization of genetic resources and promote appropriate access to such resources, as internationally agreed</t>
   </si>
   <si>
+    <t>15.7.1</t>
+  </si>
+  <si>
+    <t>Proportion of traded wildlife that was poached or illicitly trafficked</t>
+  </si>
+  <si>
+    <t>15.7</t>
+  </si>
+  <si>
+    <t>Take urgent action to end poaching and trafficking of protected species of flora and fauna and address both demand and supply of illegal wildlife products</t>
+  </si>
+  <si>
     <t>15.8.1</t>
   </si>
   <si>
@@ -1858,6 +2008,15 @@
     <t>Mobilize significant resources from all sources and at all levels to finance sustainable forest management and provide adequate incentives to developing countries to advance such management, including for conservation and reforestation</t>
   </si>
   <si>
+    <t>15.c.1</t>
+  </si>
+  <si>
+    <t>15.c</t>
+  </si>
+  <si>
+    <t>Enhance global support for efforts to combat poaching and trafficking of protected species, including by increasing the capacity of local communities to pursue sustainable livelihood opportunities</t>
+  </si>
+  <si>
     <t>16.1.1</t>
   </si>
   <si>
@@ -1870,10 +2029,16 @@
     <t>Significantly reduce all forms of violence and related death rates everywhere</t>
   </si>
   <si>
+    <t>16.1.2</t>
+  </si>
+  <si>
+    <t>Conflict-related deaths per 100,000 population, by sex, age and cause</t>
+  </si>
+  <si>
     <t>16.1.3</t>
   </si>
   <si>
-    <t>Proportion of population subjected to (a) physical violence, (b) psychological violence and (c) sexual violence in the previous 12 months</t>
+    <t>Proportion of population subjected to (a) physical violence, (b) psychological violence and (c) sexual violence in the previous 12 months</t>
   </si>
   <si>
     <t>16.1.4</t>
@@ -1882,12 +2047,6 @@
     <t>Proportion of population that feel safe walking alone around the area they live</t>
   </si>
   <si>
-    <t>16.1.2</t>
-  </si>
-  <si>
-    <t>Conflict-related deaths per 100,000 population, by sex, age and cause</t>
-  </si>
-  <si>
     <t>16.2.1</t>
   </si>
   <si>
@@ -1912,22 +2071,40 @@
     <t>Proportion of young women and men aged 18-29 years who experienced sexual violence by age 18</t>
   </si>
   <si>
+    <t>16.3.1</t>
+  </si>
+  <si>
+    <t>Proportion of victims of violence in the previous 12 months who reported their victimization to competent authorities or other officially recognized conflict resolution mechanisms</t>
+  </si>
+  <si>
+    <t>16.3</t>
+  </si>
+  <si>
+    <t>Promote the rule of law at the national and international levels and ensure equal access to justice for all</t>
+  </si>
+  <si>
     <t>16.3.2</t>
   </si>
   <si>
     <t>Unsentenced detainees as a proportion of overall prison population</t>
   </si>
   <si>
-    <t>16.3</t>
-  </si>
-  <si>
-    <t>Promote the rule of law at the national and international levels and ensure equal access to justice for all</t>
-  </si>
-  <si>
-    <t>16.3.1</t>
-  </si>
-  <si>
-    <t>Proportion of victims of violence in the previous 12 months who reported their victimization to competent authorities or other officially recognized conflict resolution mechanisms</t>
+    <t>16.3.3</t>
+  </si>
+  <si>
+    <t>Proportion of the population who have experienced a dispute in the past two years and who accessed a formal or informal dispute resolution mechanism, by type of mechanism</t>
+  </si>
+  <si>
+    <t>16.4.1</t>
+  </si>
+  <si>
+    <t>Total value of inward and outward illicit financial flows (in current United States dollars)</t>
+  </si>
+  <si>
+    <t>16.4</t>
+  </si>
+  <si>
+    <t>By 2030, significantly reduce illicit financial and arms flows, strengthen the recovery and return of stolen assets and combat all forms of organized crime</t>
   </si>
   <si>
     <t>16.4.2</t>
@@ -1936,10 +2113,16 @@
     <t>Proportion of seized, found or surrendered arms whose illicit origin or context has been traced or established by a competent authority in line with international instruments</t>
   </si>
   <si>
-    <t>16.4</t>
-  </si>
-  <si>
-    <t>By 2030, significantly reduce illicit financial and arms flows, strengthen the recovery and return of stolen assets and combat all forms of organized crime</t>
+    <t>16.5.1</t>
+  </si>
+  <si>
+    <t>Proportion of persons who had at least one contact with a public official and who paid a bribe to a public official, or were asked for a bribe by those public officials, during the previous 12 months</t>
+  </si>
+  <si>
+    <t>16.5</t>
+  </si>
+  <si>
+    <t>Substantially reduce corruption and bribery in all their forms</t>
   </si>
   <si>
     <t>16.5.2</t>
@@ -1948,18 +2131,6 @@
     <t>Proportion of businesses that had at least one contact with a public official and that paid a bribe to a public official, or were asked for a bribe by those public officials during the previous 12 months</t>
   </si>
   <si>
-    <t>16.5</t>
-  </si>
-  <si>
-    <t>Substantially reduce corruption and bribery in all their forms</t>
-  </si>
-  <si>
-    <t>16.5.1</t>
-  </si>
-  <si>
-    <t>Proportion of persons who had at least one contact with a public official and who paid a bribe to a public official, or were asked for a bribe by those public officials, during the previous 12 months</t>
-  </si>
-  <si>
     <t>16.6.1</t>
   </si>
   <si>
@@ -1972,6 +2143,12 @@
     <t>Develop effective, accountable and transparent institutions at all levels</t>
   </si>
   <si>
+    <t>16.6.2</t>
+  </si>
+  <si>
+    <t>Proportion of population satisfied with their last experience of public services</t>
+  </si>
+  <si>
     <t>16.7.1</t>
   </si>
   <si>
@@ -1984,6 +2161,12 @@
     <t>Ensure responsive, inclusive, participatory and representative decision-making at all levels</t>
   </si>
   <si>
+    <t>16.7.2</t>
+  </si>
+  <si>
+    <t>Proportion of population who believe decision-making is inclusive and responsive, by sex, age, disability and population group</t>
+  </si>
+  <si>
     <t>16.8.1</t>
   </si>
   <si>
@@ -2074,24 +2257,24 @@
     <t>Developed countries to implement fully their official development assistance commitments, including the commitment by many developed countries to achieve the target of 0.7 per cent of gross national income for official development assistance (ODA/GNI) to developing countries and 0.15 to 0.20 per cent of ODA/GNI to least developed countries; ODA providers are encouraged to consider setting a target to provide at least 0.20 per cent of ODA/GNI to least developed countries</t>
   </si>
   <si>
+    <t>17.3.1</t>
+  </si>
+  <si>
+    <t>Foreign direct investment, official development assistance and South-South cooperation as a proportion of gross national income</t>
+  </si>
+  <si>
+    <t>17.3</t>
+  </si>
+  <si>
+    <t>Mobilize additional financial resources for developing countries from multiple sources</t>
+  </si>
+  <si>
     <t>17.3.2</t>
   </si>
   <si>
     <t>Volume of remittances (in United States dollars) as a proportion of total GDP</t>
   </si>
   <si>
-    <t>17.3</t>
-  </si>
-  <si>
-    <t>Mobilize additional financial resources for developing countries from multiple sources</t>
-  </si>
-  <si>
-    <t>17.3.1</t>
-  </si>
-  <si>
-    <t>Foreign direct investment, official development assistance and South-South cooperation as a proportion of gross national income</t>
-  </si>
-  <si>
     <t>17.4.1</t>
   </si>
   <si>
@@ -2128,6 +2311,18 @@
     <t>Enhance North-South, South-South and triangular regional and international cooperation on and access to science, technology and innovation and enhance knowledge-sharing on mutually agreed terms, including through improved coordination among existing mechanisms, in particular at the United Nations level, and through a global technology facilitation mechanism</t>
   </si>
   <si>
+    <t>17.7.1</t>
+  </si>
+  <si>
+    <t>Total amount of funding for developing countries to promote the development, transfer, dissemination and diffusion of environmentally sound technologies</t>
+  </si>
+  <si>
+    <t>17.7</t>
+  </si>
+  <si>
+    <t>Promote the development, transfer, dissemination and diffusion of environmentally sound technologies to developing countries on favourable terms, including on concessional and preferential terms, as mutually agreed</t>
+  </si>
+  <si>
     <t>17.8.1</t>
   </si>
   <si>
@@ -2188,6 +2383,18 @@
     <t>Realize timely implementation of duty-free and quota-free market access on a lasting basis for all least developed countries, consistent with World Trade Organization decisions, including by ensuring that preferential rules of origin applicable to imports from least developed countries are transparent and simple, and contribute to facilitating market access</t>
   </si>
   <si>
+    <t>17.13.1</t>
+  </si>
+  <si>
+    <t>Macroeconomic Dashboard</t>
+  </si>
+  <si>
+    <t>17.13</t>
+  </si>
+  <si>
+    <t>Enhance global macroeconomic stability, including through policy coordination and policy coherence</t>
+  </si>
+  <si>
     <t>17.14.1</t>
   </si>
   <si>
@@ -2236,16 +2443,22 @@
     <t>Encourage and promote effective public, public-private and civil society partnerships, building on the experience and resourcing strategies of partnerships</t>
   </si>
   <si>
+    <t>17.18.1</t>
+  </si>
+  <si>
+    <t>Statistical capacity indicator for Sustainable Development Goal monitoring</t>
+  </si>
+  <si>
+    <t>17.18</t>
+  </si>
+  <si>
+    <t>By 2020, enhance capacity-building support to developing countries, including for least developed countries and small island developing States, to increase significantly the availability of high-quality, timely and reliable data disaggregated by income, gender, age, race, ethnicity, migratory status, disability, geographic location and other characteristics relevant in national contexts</t>
+  </si>
+  <si>
     <t>17.18.2</t>
   </si>
   <si>
     <t>Number of countries that have national statistical legislation that complies with the Fundamental Principles of Official Statistics</t>
-  </si>
-  <si>
-    <t>17.18</t>
-  </si>
-  <si>
-    <t>By 2020, enhance capacity-building support to developing countries, including for least developed countries and small island developing States, to increase significantly the availability of high-quality, timely and reliable data disaggregated by income, gender, age, race, ethnicity, migratory status, disability, geographic location and other characteristics relevant in national contexts</t>
   </si>
   <si>
     <t>17.18.3</t>
@@ -2601,7 +2814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G225"/>
+  <dimension ref="A1:G248"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2859,27 +3072,27 @@
         <v>9</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F15" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" t="s">
         <v>50</v>
       </c>
-      <c r="B16" t="s">
+      <c r="F16" t="s">
         <v>51</v>
-      </c>
-      <c r="D16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2893,44 +3106,44 @@
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" t="s">
         <v>56</v>
       </c>
-      <c r="B18" t="s">
+      <c r="F18" t="s">
         <v>57</v>
-      </c>
-      <c r="D18" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
         <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2944,27 +3157,27 @@
         <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" t="s">
         <v>64</v>
       </c>
-      <c r="B21" t="s">
+      <c r="F21" t="s">
         <v>65</v>
-      </c>
-      <c r="D21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" t="s">
-        <v>66</v>
-      </c>
-      <c r="F21" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2978,78 +3191,78 @@
         <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F22" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
         <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" t="s">
         <v>74</v>
       </c>
-      <c r="B24" t="s">
+      <c r="F24" t="s">
         <v>75</v>
-      </c>
-      <c r="D24" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" t="s">
-        <v>72</v>
-      </c>
-      <c r="F24" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D25" t="s">
         <v>9</v>
       </c>
       <c r="E25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" t="s">
         <v>80</v>
       </c>
-      <c r="B26" t="s">
+      <c r="F26" t="s">
         <v>81</v>
-      </c>
-      <c r="D26" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" t="s">
-        <v>82</v>
-      </c>
-      <c r="F26" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -3080,231 +3293,231 @@
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F28" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D29" t="s">
         <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F29" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" t="s">
         <v>94</v>
       </c>
-      <c r="B30" t="s">
+      <c r="F30" t="s">
         <v>95</v>
-      </c>
-      <c r="D30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" t="s">
-        <v>92</v>
-      </c>
-      <c r="F30" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D31" t="s">
         <v>9</v>
       </c>
       <c r="E31" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F31" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" t="s">
+        <v>103</v>
+      </c>
+      <c r="D32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" t="s">
         <v>100</v>
       </c>
-      <c r="B32" t="s">
+      <c r="F32" t="s">
         <v>101</v>
-      </c>
-      <c r="D32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" t="s">
-        <v>98</v>
-      </c>
-      <c r="F32" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
         <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F33" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F34" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" t="s">
         <v>106</v>
       </c>
-      <c r="B35" t="s">
+      <c r="F35" t="s">
         <v>107</v>
-      </c>
-      <c r="D35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" t="s">
-        <v>98</v>
-      </c>
-      <c r="F35" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D36" t="s">
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F36" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F37" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B38" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
       </c>
       <c r="E38" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F38" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" t="s">
+        <v>121</v>
+      </c>
+      <c r="D39" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" t="s">
         <v>118</v>
       </c>
-      <c r="B39" t="s">
+      <c r="F39" t="s">
         <v>119</v>
-      </c>
-      <c r="D39" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" t="s">
-        <v>116</v>
-      </c>
-      <c r="F39" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D40" t="s">
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F40" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
+        <v>126</v>
+      </c>
+      <c r="B41" t="s">
+        <v>127</v>
+      </c>
+      <c r="D41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" t="s">
         <v>124</v>
       </c>
-      <c r="B41" t="s">
+      <c r="F41" t="s">
         <v>125</v>
-      </c>
-      <c r="D41" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" t="s">
-        <v>126</v>
-      </c>
-      <c r="F41" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -3318,103 +3531,103 @@
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F42" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B43" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D43" t="s">
         <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F43" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
+        <v>136</v>
+      </c>
+      <c r="B44" t="s">
+        <v>137</v>
+      </c>
+      <c r="D44" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" t="s">
         <v>134</v>
       </c>
-      <c r="B44" t="s">
+      <c r="F44" t="s">
         <v>135</v>
-      </c>
-      <c r="D44" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" t="s">
-        <v>132</v>
-      </c>
-      <c r="F44" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B45" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D45" t="s">
         <v>9</v>
       </c>
       <c r="E45" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F45" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
+        <v>142</v>
+      </c>
+      <c r="B46" t="s">
+        <v>143</v>
+      </c>
+      <c r="D46" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" t="s">
         <v>140</v>
       </c>
-      <c r="B46" t="s">
+      <c r="F46" t="s">
         <v>141</v>
-      </c>
-      <c r="D46" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" t="s">
-        <v>138</v>
-      </c>
-      <c r="F46" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B47" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D47" t="s">
         <v>9</v>
       </c>
       <c r="E47" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="F47" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B48" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D48" t="s">
         <v>9</v>
@@ -3428,19 +3641,19 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B49" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D49" t="s">
         <v>9</v>
       </c>
       <c r="E49" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F49" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -3454,35 +3667,35 @@
         <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F50" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B51" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D51" t="s">
         <v>9</v>
       </c>
       <c r="E51" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="F51" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B52" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D52" t="s">
         <v>9</v>
@@ -3496,19 +3709,19 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B53" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D53" t="s">
         <v>9</v>
       </c>
       <c r="E53" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F53" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -3522,112 +3735,112 @@
         <v>9</v>
       </c>
       <c r="E54" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F54" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B55" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D55" t="s">
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F55" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
+        <v>172</v>
+      </c>
+      <c r="B56" t="s">
+        <v>173</v>
+      </c>
+      <c r="D56" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" t="s">
         <v>170</v>
       </c>
-      <c r="B56" t="s">
+      <c r="F56" t="s">
         <v>171</v>
-      </c>
-      <c r="D56" t="s">
-        <v>9</v>
-      </c>
-      <c r="E56" t="s">
-        <v>168</v>
-      </c>
-      <c r="F56" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B57" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D57" t="s">
         <v>9</v>
       </c>
       <c r="E57" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F57" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
+        <v>178</v>
+      </c>
+      <c r="B58" t="s">
+        <v>179</v>
+      </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" t="s">
         <v>176</v>
       </c>
-      <c r="B58" t="s">
+      <c r="F58" t="s">
         <v>177</v>
-      </c>
-      <c r="D58" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" t="s">
-        <v>174</v>
-      </c>
-      <c r="F58" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B59" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D59" t="s">
         <v>9</v>
       </c>
       <c r="E59" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F59" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
+        <v>184</v>
+      </c>
+      <c r="B60" t="s">
+        <v>185</v>
+      </c>
+      <c r="D60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" t="s">
         <v>182</v>
       </c>
-      <c r="B60" t="s">
+      <c r="F60" t="s">
         <v>183</v>
-      </c>
-      <c r="D60" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" t="s">
-        <v>184</v>
-      </c>
-      <c r="F60" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -3777,44 +3990,44 @@
         <v>9</v>
       </c>
       <c r="E69" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F69" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B70" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D70" t="s">
         <v>9</v>
       </c>
       <c r="E70" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F70" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
+        <v>226</v>
+      </c>
+      <c r="B71" t="s">
+        <v>227</v>
+      </c>
+      <c r="D71" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71" t="s">
         <v>224</v>
       </c>
-      <c r="B71" t="s">
+      <c r="F71" t="s">
         <v>225</v>
-      </c>
-      <c r="D71" t="s">
-        <v>9</v>
-      </c>
-      <c r="E71" t="s">
-        <v>226</v>
-      </c>
-      <c r="F71" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -3828,27 +4041,27 @@
         <v>9</v>
       </c>
       <c r="E72" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F72" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
+        <v>232</v>
+      </c>
+      <c r="B73" t="s">
+        <v>233</v>
+      </c>
+      <c r="D73" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" t="s">
         <v>230</v>
       </c>
-      <c r="B73" t="s">
+      <c r="F73" t="s">
         <v>231</v>
-      </c>
-      <c r="D73" t="s">
-        <v>9</v>
-      </c>
-      <c r="E73" t="s">
-        <v>232</v>
-      </c>
-      <c r="F73" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -3862,78 +4075,78 @@
         <v>9</v>
       </c>
       <c r="E74" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F74" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B75" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D75" t="s">
         <v>9</v>
       </c>
       <c r="E75" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F75" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
+        <v>242</v>
+      </c>
+      <c r="B76" t="s">
+        <v>243</v>
+      </c>
+      <c r="D76" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" t="s">
         <v>240</v>
       </c>
-      <c r="B76" t="s">
+      <c r="F76" t="s">
         <v>241</v>
-      </c>
-      <c r="D76" t="s">
-        <v>9</v>
-      </c>
-      <c r="E76" t="s">
-        <v>238</v>
-      </c>
-      <c r="F76" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B77" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D77" t="s">
         <v>9</v>
       </c>
       <c r="E77" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F77" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
+        <v>248</v>
+      </c>
+      <c r="B78" t="s">
+        <v>249</v>
+      </c>
+      <c r="D78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" t="s">
         <v>246</v>
       </c>
-      <c r="B78" t="s">
+      <c r="F78" t="s">
         <v>247</v>
-      </c>
-      <c r="D78" t="s">
-        <v>9</v>
-      </c>
-      <c r="E78" t="s">
-        <v>248</v>
-      </c>
-      <c r="F78" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -3964,44 +4177,44 @@
         <v>9</v>
       </c>
       <c r="E80" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F80" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
+        <v>256</v>
+      </c>
+      <c r="B81" t="s">
+        <v>257</v>
+      </c>
+      <c r="D81" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" t="s">
         <v>258</v>
       </c>
-      <c r="B81" t="s">
+      <c r="F81" t="s">
         <v>259</v>
-      </c>
-      <c r="D81" t="s">
-        <v>9</v>
-      </c>
-      <c r="E81" t="s">
-        <v>260</v>
-      </c>
-      <c r="F81" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
+        <v>260</v>
+      </c>
+      <c r="B82" t="s">
+        <v>261</v>
+      </c>
+      <c r="D82" t="s">
+        <v>9</v>
+      </c>
+      <c r="E82" t="s">
         <v>262</v>
       </c>
-      <c r="B82" t="s">
+      <c r="F82" t="s">
         <v>263</v>
-      </c>
-      <c r="D82" t="s">
-        <v>9</v>
-      </c>
-      <c r="E82" t="s">
-        <v>260</v>
-      </c>
-      <c r="F82" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -4032,78 +4245,78 @@
         <v>9</v>
       </c>
       <c r="E84" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F84" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B85" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D85" t="s">
         <v>9</v>
       </c>
       <c r="E85" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F85" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
+        <v>276</v>
+      </c>
+      <c r="B86" t="s">
+        <v>277</v>
+      </c>
+      <c r="D86" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" t="s">
         <v>274</v>
       </c>
-      <c r="B86" t="s">
+      <c r="F86" t="s">
         <v>275</v>
-      </c>
-      <c r="D86" t="s">
-        <v>9</v>
-      </c>
-      <c r="E86" t="s">
-        <v>272</v>
-      </c>
-      <c r="F86" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B87" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D87" t="s">
         <v>9</v>
       </c>
       <c r="E87" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F87" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
+        <v>282</v>
+      </c>
+      <c r="B88" t="s">
+        <v>283</v>
+      </c>
+      <c r="D88" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" t="s">
         <v>280</v>
       </c>
-      <c r="B88" t="s">
+      <c r="F88" t="s">
         <v>281</v>
-      </c>
-      <c r="D88" t="s">
-        <v>9</v>
-      </c>
-      <c r="E88" t="s">
-        <v>282</v>
-      </c>
-      <c r="F88" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -4134,27 +4347,27 @@
         <v>9</v>
       </c>
       <c r="E90" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F90" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
+        <v>290</v>
+      </c>
+      <c r="B91" t="s">
+        <v>291</v>
+      </c>
+      <c r="D91" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" t="s">
         <v>292</v>
       </c>
-      <c r="B91" t="s">
+      <c r="F91" t="s">
         <v>293</v>
-      </c>
-      <c r="D91" t="s">
-        <v>9</v>
-      </c>
-      <c r="E91" t="s">
-        <v>290</v>
-      </c>
-      <c r="F91" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -4219,78 +4432,78 @@
         <v>9</v>
       </c>
       <c r="E95" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F95" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
+        <v>308</v>
+      </c>
+      <c r="B96" t="s">
+        <v>309</v>
+      </c>
+      <c r="D96" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" t="s">
         <v>310</v>
       </c>
-      <c r="B96" t="s">
+      <c r="F96" t="s">
         <v>311</v>
-      </c>
-      <c r="D96" t="s">
-        <v>9</v>
-      </c>
-      <c r="E96" t="s">
-        <v>312</v>
-      </c>
-      <c r="F96" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
+        <v>312</v>
+      </c>
+      <c r="B97" t="s">
+        <v>313</v>
+      </c>
+      <c r="D97" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97" t="s">
         <v>314</v>
       </c>
-      <c r="B97" t="s">
+      <c r="F97" t="s">
         <v>315</v>
-      </c>
-      <c r="D97" t="s">
-        <v>9</v>
-      </c>
-      <c r="E97" t="s">
-        <v>316</v>
-      </c>
-      <c r="F97" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
+        <v>316</v>
+      </c>
+      <c r="B98" t="s">
+        <v>317</v>
+      </c>
+      <c r="D98" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" t="s">
         <v>318</v>
       </c>
-      <c r="B98" t="s">
+      <c r="F98" t="s">
         <v>319</v>
-      </c>
-      <c r="D98" t="s">
-        <v>9</v>
-      </c>
-      <c r="E98" t="s">
-        <v>320</v>
-      </c>
-      <c r="F98" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
+        <v>320</v>
+      </c>
+      <c r="B99" t="s">
+        <v>321</v>
+      </c>
+      <c r="D99" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99" t="s">
         <v>322</v>
       </c>
-      <c r="B99" t="s">
+      <c r="F99" t="s">
         <v>323</v>
-      </c>
-      <c r="D99" t="s">
-        <v>9</v>
-      </c>
-      <c r="E99" t="s">
-        <v>320</v>
-      </c>
-      <c r="F99" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -4321,61 +4534,61 @@
         <v>9</v>
       </c>
       <c r="E101" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F101" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B102" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D102" t="s">
         <v>9</v>
       </c>
       <c r="E102" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F102" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B103" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D103" t="s">
         <v>9</v>
       </c>
       <c r="E103" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F103" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
+        <v>340</v>
+      </c>
+      <c r="B104" t="s">
+        <v>341</v>
+      </c>
+      <c r="D104" t="s">
+        <v>9</v>
+      </c>
+      <c r="E104" t="s">
         <v>338</v>
       </c>
-      <c r="B104" t="s">
+      <c r="F104" t="s">
         <v>339</v>
-      </c>
-      <c r="D104" t="s">
-        <v>9</v>
-      </c>
-      <c r="E104" t="s">
-        <v>340</v>
-      </c>
-      <c r="F104" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -4457,27 +4670,27 @@
         <v>9</v>
       </c>
       <c r="E109" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F109" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
+        <v>360</v>
+      </c>
+      <c r="B110" t="s">
+        <v>361</v>
+      </c>
+      <c r="D110" t="s">
+        <v>9</v>
+      </c>
+      <c r="E110" t="s">
         <v>358</v>
       </c>
-      <c r="B110" t="s">
+      <c r="F110" t="s">
         <v>359</v>
-      </c>
-      <c r="D110" t="s">
-        <v>9</v>
-      </c>
-      <c r="E110" t="s">
-        <v>360</v>
-      </c>
-      <c r="F110" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -4559,78 +4772,78 @@
         <v>9</v>
       </c>
       <c r="E115" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F115" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D116" t="s">
         <v>9</v>
       </c>
       <c r="E116" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F116" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
+        <v>384</v>
+      </c>
+      <c r="B117" t="s">
+        <v>385</v>
+      </c>
+      <c r="D117" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117" t="s">
         <v>382</v>
       </c>
-      <c r="B117" t="s">
+      <c r="F117" t="s">
         <v>383</v>
-      </c>
-      <c r="D117" t="s">
-        <v>9</v>
-      </c>
-      <c r="E117" t="s">
-        <v>380</v>
-      </c>
-      <c r="F117" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B118" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D118" t="s">
         <v>9</v>
       </c>
       <c r="E118" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F118" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
+        <v>390</v>
+      </c>
+      <c r="B119" t="s">
+        <v>391</v>
+      </c>
+      <c r="D119" t="s">
+        <v>9</v>
+      </c>
+      <c r="E119" t="s">
         <v>388</v>
       </c>
-      <c r="B119" t="s">
+      <c r="F119" t="s">
         <v>389</v>
-      </c>
-      <c r="D119" t="s">
-        <v>9</v>
-      </c>
-      <c r="E119" t="s">
-        <v>390</v>
-      </c>
-      <c r="F119" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -4644,27 +4857,27 @@
         <v>9</v>
       </c>
       <c r="E120" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F120" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
+        <v>396</v>
+      </c>
+      <c r="B121" t="s">
+        <v>397</v>
+      </c>
+      <c r="D121" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" t="s">
         <v>394</v>
       </c>
-      <c r="B121" t="s">
+      <c r="F121" t="s">
         <v>395</v>
-      </c>
-      <c r="D121" t="s">
-        <v>9</v>
-      </c>
-      <c r="E121" t="s">
-        <v>396</v>
-      </c>
-      <c r="F121" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -4712,78 +4925,78 @@
         <v>9</v>
       </c>
       <c r="E124" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="F124" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
+        <v>408</v>
+      </c>
+      <c r="B125" t="s">
+        <v>409</v>
+      </c>
+      <c r="D125" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125" t="s">
         <v>410</v>
       </c>
-      <c r="B125" t="s">
+      <c r="F125" t="s">
         <v>411</v>
-      </c>
-      <c r="D125" t="s">
-        <v>9</v>
-      </c>
-      <c r="E125" t="s">
-        <v>412</v>
-      </c>
-      <c r="F125" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
+        <v>412</v>
+      </c>
+      <c r="B126" t="s">
+        <v>413</v>
+      </c>
+      <c r="D126" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" t="s">
         <v>414</v>
       </c>
-      <c r="B126" t="s">
+      <c r="F126" t="s">
         <v>415</v>
-      </c>
-      <c r="D126" t="s">
-        <v>9</v>
-      </c>
-      <c r="E126" t="s">
-        <v>416</v>
-      </c>
-      <c r="F126" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
+        <v>416</v>
+      </c>
+      <c r="B127" t="s">
+        <v>417</v>
+      </c>
+      <c r="D127" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" t="s">
         <v>418</v>
       </c>
-      <c r="B127" t="s">
+      <c r="F127" t="s">
         <v>419</v>
-      </c>
-      <c r="D127" t="s">
-        <v>9</v>
-      </c>
-      <c r="E127" t="s">
-        <v>420</v>
-      </c>
-      <c r="F127" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
+        <v>420</v>
+      </c>
+      <c r="B128" t="s">
+        <v>421</v>
+      </c>
+      <c r="D128" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" t="s">
         <v>422</v>
       </c>
-      <c r="B128" t="s">
+      <c r="F128" t="s">
         <v>423</v>
-      </c>
-      <c r="D128" t="s">
-        <v>9</v>
-      </c>
-      <c r="E128" t="s">
-        <v>420</v>
-      </c>
-      <c r="F128" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -4865,61 +5078,61 @@
         <v>9</v>
       </c>
       <c r="E133" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="F133" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B134" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D134" t="s">
         <v>9</v>
       </c>
       <c r="E134" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F134" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B135" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D135" t="s">
         <v>9</v>
       </c>
       <c r="E135" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F135" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
+        <v>450</v>
+      </c>
+      <c r="B136" t="s">
+        <v>451</v>
+      </c>
+      <c r="D136" t="s">
+        <v>9</v>
+      </c>
+      <c r="E136" t="s">
         <v>448</v>
       </c>
-      <c r="B136" t="s">
+      <c r="F136" t="s">
         <v>449</v>
-      </c>
-      <c r="D136" t="s">
-        <v>9</v>
-      </c>
-      <c r="E136" t="s">
-        <v>450</v>
-      </c>
-      <c r="F136" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -4933,256 +5146,256 @@
         <v>9</v>
       </c>
       <c r="E137" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="F137" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B138" t="s">
-        <v>29</v>
+        <v>455</v>
       </c>
       <c r="D138" t="s">
         <v>9</v>
       </c>
       <c r="E138" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="F138" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
+        <v>456</v>
+      </c>
+      <c r="B139" t="s">
+        <v>457</v>
+      </c>
+      <c r="D139" t="s">
+        <v>9</v>
+      </c>
+      <c r="E139" t="s">
+        <v>458</v>
+      </c>
+      <c r="F139" t="s">
         <v>459</v>
-      </c>
-      <c r="B139" t="s">
-        <v>460</v>
-      </c>
-      <c r="D139" t="s">
-        <v>9</v>
-      </c>
-      <c r="E139" t="s">
-        <v>457</v>
-      </c>
-      <c r="F139" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
+        <v>460</v>
+      </c>
+      <c r="B140" t="s">
         <v>461</v>
       </c>
-      <c r="B140" t="s">
+      <c r="D140" t="s">
+        <v>9</v>
+      </c>
+      <c r="E140" t="s">
         <v>462</v>
       </c>
-      <c r="D140" t="s">
-        <v>9</v>
-      </c>
-      <c r="E140" t="s">
+      <c r="F140" t="s">
         <v>463</v>
-      </c>
-      <c r="F140" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
+        <v>464</v>
+      </c>
+      <c r="B141" t="s">
         <v>465</v>
       </c>
-      <c r="B141" t="s">
+      <c r="D141" t="s">
+        <v>9</v>
+      </c>
+      <c r="E141" t="s">
         <v>466</v>
       </c>
-      <c r="D141" t="s">
-        <v>9</v>
-      </c>
-      <c r="E141" t="s">
-        <v>463</v>
-      </c>
       <c r="F141" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B142" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D142" t="s">
         <v>9</v>
       </c>
       <c r="E142" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F142" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B143" t="s">
-        <v>35</v>
+        <v>473</v>
       </c>
       <c r="D143" t="s">
         <v>9</v>
       </c>
       <c r="E143" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F143" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B144" t="s">
-        <v>37</v>
+        <v>477</v>
       </c>
       <c r="D144" t="s">
         <v>9</v>
       </c>
       <c r="E144" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="F144" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B145" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D145" t="s">
         <v>9</v>
       </c>
       <c r="E145" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F145" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B146" t="s">
-        <v>319</v>
+        <v>483</v>
       </c>
       <c r="D146" t="s">
         <v>9</v>
       </c>
       <c r="E146" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="F146" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B147" t="s">
-        <v>323</v>
+        <v>29</v>
       </c>
       <c r="D147" t="s">
         <v>9</v>
       </c>
       <c r="E147" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="F147" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B148" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="D148" t="s">
         <v>9</v>
       </c>
       <c r="E148" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F148" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B149" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="D149" t="s">
         <v>9</v>
       </c>
       <c r="E149" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="F149" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B150" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D150" t="s">
         <v>9</v>
       </c>
       <c r="E150" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="F150" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B151" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="D151" t="s">
         <v>9</v>
       </c>
       <c r="E151" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F151" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B152" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="D152" t="s">
         <v>9</v>
@@ -5196,231 +5409,231 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B153" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D153" t="s">
         <v>9</v>
       </c>
       <c r="E153" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F153" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B154" t="s">
-        <v>307</v>
+        <v>35</v>
       </c>
       <c r="D154" t="s">
         <v>9</v>
       </c>
       <c r="E154" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F154" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
+        <v>510</v>
+      </c>
+      <c r="B155" t="s">
+        <v>37</v>
+      </c>
+      <c r="D155" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" t="s">
         <v>508</v>
       </c>
-      <c r="B155" t="s">
+      <c r="F155" t="s">
         <v>509</v>
-      </c>
-      <c r="D155" t="s">
-        <v>9</v>
-      </c>
-      <c r="E155" t="s">
-        <v>510</v>
-      </c>
-      <c r="F155" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
+        <v>511</v>
+      </c>
+      <c r="B156" t="s">
         <v>512</v>
       </c>
-      <c r="B156" t="s">
+      <c r="D156" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" t="s">
         <v>513</v>
       </c>
-      <c r="D156" t="s">
-        <v>9</v>
-      </c>
-      <c r="E156" t="s">
+      <c r="F156" t="s">
         <v>514</v>
-      </c>
-      <c r="F156" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
+        <v>515</v>
+      </c>
+      <c r="B157" t="s">
+        <v>337</v>
+      </c>
+      <c r="D157" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" t="s">
         <v>516</v>
       </c>
-      <c r="B157" t="s">
-        <v>29</v>
-      </c>
-      <c r="D157" t="s">
-        <v>9</v>
-      </c>
-      <c r="E157" t="s">
+      <c r="F157" t="s">
         <v>517</v>
-      </c>
-      <c r="F157" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B158" t="s">
-        <v>35</v>
+        <v>341</v>
       </c>
       <c r="D158" t="s">
         <v>9</v>
       </c>
       <c r="E158" t="s">
+        <v>516</v>
+      </c>
+      <c r="F158" t="s">
         <v>517</v>
-      </c>
-      <c r="F158" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
+        <v>519</v>
+      </c>
+      <c r="B159" t="s">
         <v>520</v>
       </c>
-      <c r="B159" t="s">
-        <v>37</v>
-      </c>
       <c r="D159" t="s">
         <v>9</v>
       </c>
       <c r="E159" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="F159" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B160" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D160" t="s">
         <v>9</v>
       </c>
       <c r="E160" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F160" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
+        <v>527</v>
+      </c>
+      <c r="B161" t="s">
+        <v>528</v>
+      </c>
+      <c r="D161" t="s">
+        <v>9</v>
+      </c>
+      <c r="E161" t="s">
         <v>525</v>
       </c>
-      <c r="B161" t="s">
+      <c r="F161" t="s">
         <v>526</v>
-      </c>
-      <c r="D161" t="s">
-        <v>9</v>
-      </c>
-      <c r="E161" t="s">
-        <v>523</v>
-      </c>
-      <c r="F161" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B162" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D162" t="s">
         <v>9</v>
       </c>
       <c r="E162" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="F162" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B163" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D163" t="s">
         <v>9</v>
       </c>
       <c r="E163" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F163" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B164" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D164" t="s">
         <v>9</v>
       </c>
       <c r="E164" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F164" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B165" t="s">
-        <v>540</v>
+        <v>203</v>
       </c>
       <c r="D165" t="s">
         <v>9</v>
       </c>
       <c r="E165" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F165" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B166" t="s">
-        <v>544</v>
+        <v>321</v>
       </c>
       <c r="D166" t="s">
         <v>9</v>
@@ -5471,968 +5684,1359 @@
         <v>555</v>
       </c>
       <c r="B169" t="s">
+        <v>29</v>
+      </c>
+      <c r="D169" t="s">
+        <v>9</v>
+      </c>
+      <c r="E169" t="s">
         <v>556</v>
       </c>
-      <c r="D169" t="s">
-        <v>9</v>
-      </c>
-      <c r="E169" t="s">
+      <c r="F169" t="s">
         <v>557</v>
-      </c>
-      <c r="F169" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B170" t="s">
-        <v>560</v>
+        <v>35</v>
       </c>
       <c r="D170" t="s">
         <v>9</v>
       </c>
       <c r="E170" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="F170" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B171" t="s">
-        <v>564</v>
+        <v>37</v>
       </c>
       <c r="D171" t="s">
         <v>9</v>
       </c>
       <c r="E171" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="F171" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="B172" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="D172" t="s">
         <v>9</v>
       </c>
       <c r="E172" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="F172" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="B173" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="D173" t="s">
         <v>9</v>
       </c>
       <c r="E173" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="F173" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="B174" t="s">
-        <v>576</v>
+        <v>203</v>
       </c>
       <c r="D174" t="s">
         <v>9</v>
       </c>
       <c r="E174" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="F174" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="B175" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="D175" t="s">
         <v>9</v>
       </c>
       <c r="E175" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="F175" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B176" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="D176" t="s">
         <v>9</v>
       </c>
       <c r="E176" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="F176" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="B177" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="D177" t="s">
         <v>9</v>
       </c>
       <c r="E177" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="F177" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="B178" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="D178" t="s">
         <v>9</v>
       </c>
       <c r="E178" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="F178" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="B179" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="D179" t="s">
         <v>9</v>
       </c>
       <c r="E179" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="F179" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="B180" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="D180" t="s">
         <v>9</v>
       </c>
       <c r="E180" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="F180" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="B181" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="D181" t="s">
         <v>9</v>
       </c>
       <c r="E181" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="F181" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="B182" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="D182" t="s">
         <v>9</v>
       </c>
       <c r="E182" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="F182" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="B183" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="D183" t="s">
         <v>9</v>
       </c>
       <c r="E183" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="F183" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B184" t="s">
+        <v>606</v>
+      </c>
+      <c r="D184" t="s">
+        <v>9</v>
+      </c>
+      <c r="E184" t="s">
+        <v>607</v>
+      </c>
+      <c r="F184" t="s">
         <v>608</v>
-      </c>
-      <c r="D184" t="s">
-        <v>9</v>
-      </c>
-      <c r="E184" t="s">
-        <v>612</v>
-      </c>
-      <c r="F184" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="B185" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="D185" t="s">
         <v>9</v>
       </c>
       <c r="E185" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="F185" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="B186" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="D186" t="s">
         <v>9</v>
       </c>
       <c r="E186" t="s">
+        <v>615</v>
+      </c>
+      <c r="F186" t="s">
         <v>616</v>
-      </c>
-      <c r="F186" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
+        <v>617</v>
+      </c>
+      <c r="B187" t="s">
+        <v>618</v>
+      </c>
+      <c r="D187" t="s">
+        <v>9</v>
+      </c>
+      <c r="E187" t="s">
+        <v>619</v>
+      </c>
+      <c r="F187" t="s">
         <v>620</v>
-      </c>
-      <c r="B187" t="s">
-        <v>621</v>
-      </c>
-      <c r="D187" t="s">
-        <v>9</v>
-      </c>
-      <c r="E187" t="s">
-        <v>616</v>
-      </c>
-      <c r="F187" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
+        <v>621</v>
+      </c>
+      <c r="B188" t="s">
         <v>622</v>
       </c>
-      <c r="B188" t="s">
-        <v>623</v>
-      </c>
       <c r="D188" t="s">
         <v>9</v>
       </c>
       <c r="E188" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="F188" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
+        <v>623</v>
+      </c>
+      <c r="B189" t="s">
         <v>624</v>
       </c>
-      <c r="B189" t="s">
+      <c r="D189" t="s">
+        <v>9</v>
+      </c>
+      <c r="E189" t="s">
         <v>625</v>
       </c>
-      <c r="D189" t="s">
-        <v>9</v>
-      </c>
-      <c r="E189" t="s">
+      <c r="F189" t="s">
         <v>626</v>
-      </c>
-      <c r="F189" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
+        <v>627</v>
+      </c>
+      <c r="B190" t="s">
         <v>628</v>
       </c>
-      <c r="B190" t="s">
+      <c r="D190" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" t="s">
         <v>629</v>
       </c>
-      <c r="D190" t="s">
-        <v>9</v>
-      </c>
-      <c r="E190" t="s">
-        <v>626</v>
-      </c>
       <c r="F190" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B191" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D191" t="s">
         <v>9</v>
       </c>
       <c r="E191" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="F191" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B192" t="s">
+        <v>636</v>
+      </c>
+      <c r="D192" t="s">
+        <v>9</v>
+      </c>
+      <c r="E192" t="s">
         <v>633</v>
       </c>
-      <c r="D192" t="s">
-        <v>9</v>
-      </c>
-      <c r="E192" t="s">
+      <c r="F192" t="s">
         <v>634</v>
-      </c>
-      <c r="F192" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B193" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D193" t="s">
         <v>9</v>
       </c>
       <c r="E193" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="F193" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B194" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D194" t="s">
         <v>9</v>
       </c>
       <c r="E194" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="F194" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B195" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="D195" t="s">
         <v>9</v>
       </c>
       <c r="E195" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="F195" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B196" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D196" t="s">
         <v>9</v>
       </c>
       <c r="E196" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="F196" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="B197" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="D197" t="s">
         <v>9</v>
       </c>
       <c r="E197" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="F197" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="B198" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="D198" t="s">
         <v>9</v>
       </c>
       <c r="E198" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="F198" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="B199" t="s">
-        <v>429</v>
+        <v>658</v>
       </c>
       <c r="D199" t="s">
         <v>9</v>
       </c>
       <c r="E199" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="F199" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="B200" t="s">
-        <v>660</v>
+        <v>646</v>
       </c>
       <c r="D200" t="s">
         <v>9</v>
       </c>
       <c r="E200" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="F200" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B201" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="D201" t="s">
         <v>9</v>
       </c>
       <c r="E201" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="F201" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="B202" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D202" t="s">
         <v>9</v>
       </c>
       <c r="E202" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="F202" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
+        <v>673</v>
+      </c>
+      <c r="B203" t="s">
+        <v>674</v>
+      </c>
+      <c r="D203" t="s">
+        <v>9</v>
+      </c>
+      <c r="E203" t="s">
         <v>669</v>
       </c>
-      <c r="B203" t="s">
+      <c r="F203" t="s">
         <v>670</v>
-      </c>
-      <c r="D203" t="s">
-        <v>9</v>
-      </c>
-      <c r="E203" t="s">
-        <v>671</v>
-      </c>
-      <c r="F203" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B204" t="s">
-        <v>415</v>
+        <v>676</v>
       </c>
       <c r="D204" t="s">
         <v>9</v>
       </c>
       <c r="E204" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="F204" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B205" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D205" t="s">
         <v>9</v>
       </c>
       <c r="E205" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F205" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
+        <v>681</v>
+      </c>
+      <c r="B206" t="s">
+        <v>682</v>
+      </c>
+      <c r="D206" t="s">
+        <v>9</v>
+      </c>
+      <c r="E206" t="s">
+        <v>679</v>
+      </c>
+      <c r="F206" t="s">
         <v>680</v>
-      </c>
-      <c r="B206" t="s">
-        <v>681</v>
-      </c>
-      <c r="D206" t="s">
-        <v>9</v>
-      </c>
-      <c r="E206" t="s">
-        <v>678</v>
-      </c>
-      <c r="F206" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B207" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D207" t="s">
         <v>9</v>
       </c>
       <c r="E207" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="F207" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" t="s">
+        <v>685</v>
+      </c>
+      <c r="B208" t="s">
         <v>686</v>
       </c>
-      <c r="B208" t="s">
+      <c r="D208" t="s">
+        <v>9</v>
+      </c>
+      <c r="E208" t="s">
         <v>687</v>
       </c>
-      <c r="D208" t="s">
-        <v>9</v>
-      </c>
-      <c r="E208" t="s">
+      <c r="F208" t="s">
         <v>688</v>
-      </c>
-      <c r="F208" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
+        <v>689</v>
+      </c>
+      <c r="B209" t="s">
         <v>690</v>
       </c>
-      <c r="B209" t="s">
-        <v>691</v>
-      </c>
       <c r="D209" t="s">
         <v>9</v>
       </c>
       <c r="E209" t="s">
+        <v>687</v>
+      </c>
+      <c r="F209" t="s">
         <v>688</v>
-      </c>
-      <c r="F209" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
+        <v>691</v>
+      </c>
+      <c r="B210" t="s">
         <v>692</v>
       </c>
-      <c r="B210" t="s">
-        <v>693</v>
-      </c>
       <c r="D210" t="s">
         <v>9</v>
       </c>
       <c r="E210" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="F210" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
+        <v>693</v>
+      </c>
+      <c r="B211" t="s">
+        <v>694</v>
+      </c>
+      <c r="D211" t="s">
+        <v>9</v>
+      </c>
+      <c r="E211" t="s">
+        <v>695</v>
+      </c>
+      <c r="F211" t="s">
         <v>696</v>
-      </c>
-      <c r="B211" t="s">
-        <v>697</v>
-      </c>
-      <c r="D211" t="s">
-        <v>9</v>
-      </c>
-      <c r="E211" t="s">
-        <v>698</v>
-      </c>
-      <c r="F211" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B212" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D212" t="s">
         <v>9</v>
       </c>
       <c r="E212" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="F212" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="B213" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="D213" t="s">
         <v>9</v>
       </c>
       <c r="E213" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="F213" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="B214" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="D214" t="s">
         <v>9</v>
       </c>
       <c r="E214" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="F214" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="B215" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="D215" t="s">
         <v>9</v>
       </c>
       <c r="E215" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="F215" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="B216" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="D216" t="s">
         <v>9</v>
       </c>
       <c r="E216" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="F216" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="B217" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="D217" t="s">
         <v>9</v>
       </c>
       <c r="E217" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="F217" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
       <c r="B218" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="D218" t="s">
         <v>9</v>
       </c>
       <c r="E218" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="F218" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="B219" t="s">
-        <v>729</v>
+        <v>443</v>
       </c>
       <c r="D219" t="s">
         <v>9</v>
       </c>
       <c r="E219" t="s">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="F219" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="B220" t="s">
-        <v>733</v>
+        <v>721</v>
       </c>
       <c r="D220" t="s">
         <v>9</v>
       </c>
       <c r="E220" t="s">
-        <v>734</v>
+        <v>722</v>
       </c>
       <c r="F220" t="s">
-        <v>735</v>
+        <v>723</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="B221" t="s">
-        <v>737</v>
+        <v>725</v>
       </c>
       <c r="D221" t="s">
         <v>9</v>
       </c>
       <c r="E221" t="s">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="F221" t="s">
-        <v>739</v>
+        <v>727</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>740</v>
+        <v>728</v>
       </c>
       <c r="B222" t="s">
-        <v>741</v>
+        <v>729</v>
       </c>
       <c r="D222" t="s">
         <v>9</v>
       </c>
       <c r="E222" t="s">
-        <v>742</v>
+        <v>726</v>
       </c>
       <c r="F222" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
-        <v>744</v>
+        <v>730</v>
       </c>
       <c r="B223" t="s">
-        <v>745</v>
+        <v>731</v>
       </c>
       <c r="D223" t="s">
         <v>9</v>
       </c>
       <c r="E223" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="F223" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="B224" t="s">
-        <v>747</v>
+        <v>429</v>
       </c>
       <c r="D224" t="s">
         <v>9</v>
       </c>
       <c r="E224" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="F224" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
     </row>
     <row r="225" spans="1:6">
       <c r="A225" t="s">
+        <v>737</v>
+      </c>
+      <c r="B225" t="s">
+        <v>738</v>
+      </c>
+      <c r="D225" t="s">
+        <v>9</v>
+      </c>
+      <c r="E225" t="s">
+        <v>739</v>
+      </c>
+      <c r="F225" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226" t="s">
+        <v>741</v>
+      </c>
+      <c r="B226" t="s">
+        <v>742</v>
+      </c>
+      <c r="D226" t="s">
+        <v>9</v>
+      </c>
+      <c r="E226" t="s">
+        <v>739</v>
+      </c>
+      <c r="F226" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
+      <c r="A227" t="s">
+        <v>743</v>
+      </c>
+      <c r="B227" t="s">
+        <v>744</v>
+      </c>
+      <c r="D227" t="s">
+        <v>9</v>
+      </c>
+      <c r="E227" t="s">
+        <v>745</v>
+      </c>
+      <c r="F227" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
+      <c r="A228" t="s">
+        <v>747</v>
+      </c>
+      <c r="B228" t="s">
+        <v>748</v>
+      </c>
+      <c r="D228" t="s">
+        <v>9</v>
+      </c>
+      <c r="E228" t="s">
+        <v>749</v>
+      </c>
+      <c r="F228" t="s">
         <v>750</v>
       </c>
-      <c r="B225" t="s">
+    </row>
+    <row r="229" spans="1:6">
+      <c r="A229" t="s">
         <v>751</v>
       </c>
-      <c r="D225" t="s">
-        <v>9</v>
-      </c>
-      <c r="E225" t="s">
-        <v>748</v>
-      </c>
-      <c r="F225" t="s">
+      <c r="B229" t="s">
+        <v>752</v>
+      </c>
+      <c r="D229" t="s">
+        <v>9</v>
+      </c>
+      <c r="E229" t="s">
         <v>749</v>
+      </c>
+      <c r="F229" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
+      <c r="A230" t="s">
+        <v>753</v>
+      </c>
+      <c r="B230" t="s">
+        <v>754</v>
+      </c>
+      <c r="D230" t="s">
+        <v>9</v>
+      </c>
+      <c r="E230" t="s">
+        <v>755</v>
+      </c>
+      <c r="F230" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231" t="s">
+        <v>757</v>
+      </c>
+      <c r="B231" t="s">
+        <v>758</v>
+      </c>
+      <c r="D231" t="s">
+        <v>9</v>
+      </c>
+      <c r="E231" t="s">
+        <v>759</v>
+      </c>
+      <c r="F231" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" t="s">
+        <v>761</v>
+      </c>
+      <c r="B232" t="s">
+        <v>762</v>
+      </c>
+      <c r="D232" t="s">
+        <v>9</v>
+      </c>
+      <c r="E232" t="s">
+        <v>763</v>
+      </c>
+      <c r="F232" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
+      <c r="A233" t="s">
+        <v>765</v>
+      </c>
+      <c r="B233" t="s">
+        <v>766</v>
+      </c>
+      <c r="D233" t="s">
+        <v>9</v>
+      </c>
+      <c r="E233" t="s">
+        <v>767</v>
+      </c>
+      <c r="F233" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234" t="s">
+        <v>769</v>
+      </c>
+      <c r="B234" t="s">
+        <v>770</v>
+      </c>
+      <c r="D234" t="s">
+        <v>9</v>
+      </c>
+      <c r="E234" t="s">
+        <v>771</v>
+      </c>
+      <c r="F234" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
+      <c r="A235" t="s">
+        <v>773</v>
+      </c>
+      <c r="B235" t="s">
+        <v>774</v>
+      </c>
+      <c r="D235" t="s">
+        <v>9</v>
+      </c>
+      <c r="E235" t="s">
+        <v>775</v>
+      </c>
+      <c r="F235" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
+      <c r="A236" t="s">
+        <v>777</v>
+      </c>
+      <c r="B236" t="s">
+        <v>778</v>
+      </c>
+      <c r="D236" t="s">
+        <v>9</v>
+      </c>
+      <c r="E236" t="s">
+        <v>779</v>
+      </c>
+      <c r="F236" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237" t="s">
+        <v>781</v>
+      </c>
+      <c r="B237" t="s">
+        <v>782</v>
+      </c>
+      <c r="D237" t="s">
+        <v>9</v>
+      </c>
+      <c r="E237" t="s">
+        <v>783</v>
+      </c>
+      <c r="F237" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238" t="s">
+        <v>785</v>
+      </c>
+      <c r="B238" t="s">
+        <v>786</v>
+      </c>
+      <c r="D238" t="s">
+        <v>9</v>
+      </c>
+      <c r="E238" t="s">
+        <v>787</v>
+      </c>
+      <c r="F238" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239" t="s">
+        <v>789</v>
+      </c>
+      <c r="B239" t="s">
+        <v>790</v>
+      </c>
+      <c r="D239" t="s">
+        <v>9</v>
+      </c>
+      <c r="E239" t="s">
+        <v>791</v>
+      </c>
+      <c r="F239" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240" t="s">
+        <v>793</v>
+      </c>
+      <c r="B240" t="s">
+        <v>794</v>
+      </c>
+      <c r="D240" t="s">
+        <v>9</v>
+      </c>
+      <c r="E240" t="s">
+        <v>795</v>
+      </c>
+      <c r="F240" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241" t="s">
+        <v>797</v>
+      </c>
+      <c r="B241" t="s">
+        <v>798</v>
+      </c>
+      <c r="D241" t="s">
+        <v>9</v>
+      </c>
+      <c r="E241" t="s">
+        <v>799</v>
+      </c>
+      <c r="F241" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242" t="s">
+        <v>801</v>
+      </c>
+      <c r="B242" t="s">
+        <v>802</v>
+      </c>
+      <c r="D242" t="s">
+        <v>9</v>
+      </c>
+      <c r="E242" t="s">
+        <v>803</v>
+      </c>
+      <c r="F242" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243" t="s">
+        <v>805</v>
+      </c>
+      <c r="B243" t="s">
+        <v>806</v>
+      </c>
+      <c r="D243" t="s">
+        <v>9</v>
+      </c>
+      <c r="E243" t="s">
+        <v>807</v>
+      </c>
+      <c r="F243" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244" t="s">
+        <v>809</v>
+      </c>
+      <c r="B244" t="s">
+        <v>810</v>
+      </c>
+      <c r="D244" t="s">
+        <v>9</v>
+      </c>
+      <c r="E244" t="s">
+        <v>811</v>
+      </c>
+      <c r="F244" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245" t="s">
+        <v>813</v>
+      </c>
+      <c r="B245" t="s">
+        <v>814</v>
+      </c>
+      <c r="D245" t="s">
+        <v>9</v>
+      </c>
+      <c r="E245" t="s">
+        <v>811</v>
+      </c>
+      <c r="F245" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246" t="s">
+        <v>815</v>
+      </c>
+      <c r="B246" t="s">
+        <v>816</v>
+      </c>
+      <c r="D246" t="s">
+        <v>9</v>
+      </c>
+      <c r="E246" t="s">
+        <v>811</v>
+      </c>
+      <c r="F246" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247" t="s">
+        <v>817</v>
+      </c>
+      <c r="B247" t="s">
+        <v>818</v>
+      </c>
+      <c r="D247" t="s">
+        <v>9</v>
+      </c>
+      <c r="E247" t="s">
+        <v>819</v>
+      </c>
+      <c r="F247" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248" t="s">
+        <v>821</v>
+      </c>
+      <c r="B248" t="s">
+        <v>822</v>
+      </c>
+      <c r="D248" t="s">
+        <v>9</v>
+      </c>
+      <c r="E248" t="s">
+        <v>819</v>
+      </c>
+      <c r="F248" t="s">
+        <v>820</v>
       </c>
     </row>
   </sheetData>

--- a/api/clv1/codelist/UNSDG-Indicators.xlsx
+++ b/api/clv1/codelist/UNSDG-Indicators.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="824">
   <si>
     <t>code</t>
   </si>
@@ -121,7 +121,7 @@
     <t>1.5.3</t>
   </si>
   <si>
-    <t>Number of countries that adopt and implement national disaster risk reduction strategies in line with the Sendai Framework for Disaster Risk Reduction 2015-2030</t>
+    <t>Number of countries that adopt and implement national disaster risk reduction strategies in line with the Sendai Framework for Disaster Risk Reduction 2015–2030</t>
   </si>
   <si>
     <t>1.5.4</t>
@@ -181,7 +181,7 @@
     <t>2.2.1</t>
   </si>
   <si>
-    <t>Prevalence of stunting (height for age &lt;-2 standard deviation from the median of the World Health Organization (WHO) Child Growth Standards) among children under 5 years of age</t>
+    <t>Prevalence of stunting (height for age &lt;-2 standard deviation from the median of the World Health Organization (WHO) Child Growth Standards) among children under 5 years of age</t>
   </si>
   <si>
     <t>2.2</t>
@@ -193,7 +193,7 @@
     <t>2.2.2</t>
   </si>
   <si>
-    <t>Prevalence of malnutrition (weight for height &gt;+2 or &lt;-2 standard deviation from the median of the WHO Child Growth Standards) among children under 5 years of age, by type (wasting and overweight)</t>
+    <t>Prevalence of malnutrition (weight for height &gt;+2 or &lt;-2 standard deviation from the median of the WHO Child Growth Standards) among children under 5 years of age, by type (wasting and overweight)</t>
   </si>
   <si>
     <t>2.2.3</t>
@@ -415,7 +415,7 @@
     <t>3.7.1</t>
   </si>
   <si>
-    <t>Proportion of women of reproductive age (aged 15-49 years) who have their need for family planning satisfied with modern methods</t>
+    <t>Proportion of women of reproductive age (aged 15–49 years) who have their need for family planning satisfied with modern methods</t>
   </si>
   <si>
     <t>3.7</t>
@@ -427,7 +427,7 @@
     <t>3.7.2</t>
   </si>
   <si>
-    <t>Adolescent birth rate (aged 10-14 years; aged 15-19 years) per 1,000 women in that age group</t>
+    <t>Adolescent birth rate (aged 10–14 years; aged 15–19 years) per 1,000 women in that age group</t>
   </si>
   <si>
     <t>3.8.1</t>
@@ -475,7 +475,7 @@
     <t>3.a.1</t>
   </si>
   <si>
-    <t>Age-standardized prevalence of current tobacco use among persons aged 15 years and older</t>
+    <t>Age-standardized prevalence of current tobacco use among persons aged 15 years and older</t>
   </si>
   <si>
     <t>3.a</t>
@@ -559,7 +559,7 @@
     <t>4.2.1</t>
   </si>
   <si>
-    <t>Proportion of children aged 24-59 months who are developmentally on track in health, learning and psychosocial well-being, by sex</t>
+    <t>Proportion of children aged 24–59 months who are developmentally on track in health, learning and psychosocial well-being, by sex</t>
   </si>
   <si>
     <t>4.2</t>
@@ -577,7 +577,7 @@
     <t>4.3.1</t>
   </si>
   <si>
-    <t>Participation rate of youth and adults in formal and non-formal education and training in the previous 12 months, by sex</t>
+    <t>Participation rate of youth and adults in formal and non-formal education and training in the previous 12 months, by sex</t>
   </si>
   <si>
     <t>4.3</t>
@@ -685,7 +685,7 @@
     <t>5.2.1</t>
   </si>
   <si>
-    <t>Proportion of ever-partnered women and girls aged 15 years and older subjected to physical, sexual or psychological violence by a current or former intimate partner in the previous 12 months, by form of violence and by age</t>
+    <t>Proportion of ever-partnered women and girls aged 15 years and older subjected to physical, sexual or psychological violence by a current or former intimate partner in the previous 12 months, by form of violence and by age</t>
   </si>
   <si>
     <t>5.2</t>
@@ -697,13 +697,13 @@
     <t>5.2.2</t>
   </si>
   <si>
-    <t>Proportion of women and girls aged 15 years and older subjected to sexual violence by persons other than an intimate partner in the previous 12 months, by age and place of occurrence</t>
+    <t>Proportion of women and girls aged 15 years and older subjected to sexual violence by persons other than an intimate partner in the previous 12 months, by age and place of occurrence</t>
   </si>
   <si>
     <t>5.3.1</t>
   </si>
   <si>
-    <t>Proportion of women aged 20-24 years who were married or in a union before age 15 and before age 18</t>
+    <t>Proportion of women aged 20–24 years who were married or in a union before age 15 and before age 18</t>
   </si>
   <si>
     <t>5.3</t>
@@ -715,7 +715,7 @@
     <t>5.3.2</t>
   </si>
   <si>
-    <t>Proportion of girls and women aged 15-49 years who have undergone female genital mutilation/cutting, by age</t>
+    <t>Proportion of girls and women aged 15–49 years who have undergone female genital mutilation/cutting, by age</t>
   </si>
   <si>
     <t>5.4.1</t>
@@ -733,7 +733,7 @@
     <t>5.5.1</t>
   </si>
   <si>
-    <t>Proportion of seats held by women in (a) national parliaments and (b) local governments</t>
+    <t>Proportion of seats held by women in (a) national parliaments and (b) local governments</t>
   </si>
   <si>
     <t>5.5</t>
@@ -751,7 +751,7 @@
     <t>5.6.1</t>
   </si>
   <si>
-    <t>Proportion of women aged 15-49 years who make their own informed decisions regarding sexual relations, contraceptive use and reproductive health care</t>
+    <t>Proportion of women aged 15–49 years who make their own informed decisions regarding sexual relations, contraceptive use and reproductive health care</t>
   </si>
   <si>
     <t>5.6</t>
@@ -1063,7 +1063,7 @@
     <t>8.6.1</t>
   </si>
   <si>
-    <t>Proportion of youth (aged 15-24 years) not in education, employment or training</t>
+    <t>Proportion of youth (aged 15–24 years) not in education, employment or training</t>
   </si>
   <si>
     <t>8.6</t>
@@ -1075,7 +1075,7 @@
     <t>8.7.1</t>
   </si>
   <si>
-    <t>Proportion and number of children aged 5-17 years engaged in child labour, by sex and age</t>
+    <t>Proportion and number of children aged 5–17 years engaged in child labour, by sex and age</t>
   </si>
   <si>
     <t>8.7</t>
@@ -1129,7 +1129,7 @@
     <t>8.10.2</t>
   </si>
   <si>
-    <t>Proportion of adults (15 years and older) with an account at a bank or other financial institution or with a mobile-money-service provider</t>
+    <t>Proportion of adults (15 years and older) with an account at a bank or other financial institution or with a mobile-money-service provider</t>
   </si>
   <si>
     <t>8.a.1</t>
@@ -1159,7 +1159,7 @@
     <t>9.1.1</t>
   </si>
   <si>
-    <t>Proportion of the rural population who live within 2 km of an all-season road</t>
+    <t>Proportion of the rural population who live within 2 km of an all-season road</t>
   </si>
   <si>
     <t>9.1</t>
@@ -1279,7 +1279,7 @@
     <t>10.1.1</t>
   </si>
   <si>
-    <t>Growth rates of household expenditure or income per capita among the bottom 40 per cent of the population and the total population</t>
+    <t>Growth rates of household expenditure or income per capita among the bottom 40 per cent of the population and the total population</t>
   </si>
   <si>
     <t>10.1</t>
@@ -1291,7 +1291,7 @@
     <t>10.2.1</t>
   </si>
   <si>
-    <t>Proportion of people living below 50 per cent of median income, by sex, age and persons with disabilities</t>
+    <t>Proportion of people living below 50 per cent of median income, by sex, age and persons with disabilities</t>
   </si>
   <si>
     <t>10.2</t>
@@ -1303,924 +1303,927 @@
     <t>10.3.1</t>
   </si>
   <si>
+    <t>Proportion of population reporting having personally felt discriminated against or harassed in the previous 12 months on the basis of a ground of discrimination prohibited under international human rights law</t>
+  </si>
+  <si>
+    <t>10.3</t>
+  </si>
+  <si>
+    <t>Ensure equal opportunity and reduce inequalities of outcome, including by eliminating discriminatory laws, policies and practices and promoting appropriate legislation, policies and action in this regard</t>
+  </si>
+  <si>
+    <t>10.4.1</t>
+  </si>
+  <si>
+    <t>Labour share of GDP</t>
+  </si>
+  <si>
+    <t>10.4</t>
+  </si>
+  <si>
+    <t>Adopt policies, especially fiscal, wage and social protection policies, and progressively achieve greater equality</t>
+  </si>
+  <si>
+    <t>10.4.2</t>
+  </si>
+  <si>
+    <t>Redistributive impact of fiscal policy</t>
+  </si>
+  <si>
+    <t>10.5.1</t>
+  </si>
+  <si>
+    <t>Financial Soundness Indicators</t>
+  </si>
+  <si>
+    <t>10.5</t>
+  </si>
+  <si>
+    <t>Improve the regulation and monitoring of global financial markets and institutions and strengthen the implementation of such regulations</t>
+  </si>
+  <si>
+    <t>10.6.1</t>
+  </si>
+  <si>
+    <t>Proportion of members and voting rights of developing countries in international organizations</t>
+  </si>
+  <si>
+    <t>10.6</t>
+  </si>
+  <si>
+    <t>Ensure enhanced representation and voice for developing countries in decision-making in global international economic and financial institutions in order to deliver more effective, credible, accountable and legitimate institutions</t>
+  </si>
+  <si>
+    <t>10.7.1</t>
+  </si>
+  <si>
+    <t>Recruitment cost borne by employee as a proportion of monthly income earned in country of destination</t>
+  </si>
+  <si>
+    <t>10.7</t>
+  </si>
+  <si>
+    <t>Facilitate orderly, safe, regular and responsible migration and mobility of people, including through the implementation of planned and well-managed migration policies</t>
+  </si>
+  <si>
+    <t>10.7.2</t>
+  </si>
+  <si>
+    <t>Number of countries with migration policies that facilitate orderly, safe, regular and responsible migration and mobility of people</t>
+  </si>
+  <si>
+    <t>10.7.3</t>
+  </si>
+  <si>
+    <t>Number of people who died or disappeared in the process of migration towards an international destination</t>
+  </si>
+  <si>
+    <t>10.7.4</t>
+  </si>
+  <si>
+    <t>Proportion of the population who are refugees, by country of origin</t>
+  </si>
+  <si>
+    <t>10.a.1</t>
+  </si>
+  <si>
+    <t>Proportion of tariff lines applied to imports from least developed countries and developing countries with zero-tariff</t>
+  </si>
+  <si>
+    <t>10.a</t>
+  </si>
+  <si>
+    <t>Implement the principle of special and differential treatment for developing countries, in particular least developed countries, in accordance with World Trade Organization agreements</t>
+  </si>
+  <si>
+    <t>10.b.1</t>
+  </si>
+  <si>
+    <t>Total resource flows for development, by recipient and donor countries and type of flow (e.g. official development assistance, foreign direct investment and other flows)</t>
+  </si>
+  <si>
+    <t>10.b</t>
+  </si>
+  <si>
+    <t>Encourage official development assistance and financial flows, including foreign direct investment, to States where the need is greatest, in particular least developed countries, African countries, small island developing States and landlocked developing countries, in accordance with their national plans and programmes</t>
+  </si>
+  <si>
+    <t>10.c.1</t>
+  </si>
+  <si>
+    <t>Remittance costs as a proportion of the amount remitted</t>
+  </si>
+  <si>
+    <t>10.c</t>
+  </si>
+  <si>
+    <t>By 2030, reduce to less than 3 per cent the transaction costs of migrant remittances and eliminate remittance corridors with costs higher than 5 per cent</t>
+  </si>
+  <si>
+    <t>11.1.1</t>
+  </si>
+  <si>
+    <t>Proportion of urban population living in slums, informal settlements or inadequate housing</t>
+  </si>
+  <si>
+    <t>11.1</t>
+  </si>
+  <si>
+    <t>By 2030, ensure access for all to adequate, safe and affordable housing and basic services and upgrade slums</t>
+  </si>
+  <si>
+    <t>11.2.1</t>
+  </si>
+  <si>
+    <t>Proportion of population that has convenient access to public transport, by sex, age and persons with disabilities</t>
+  </si>
+  <si>
+    <t>11.2</t>
+  </si>
+  <si>
+    <t>By 2030, provide access to safe, affordable, accessible and sustainable transport systems for all, improving road safety, notably by expanding public transport, with special attention to the needs of those in vulnerable situations, women, children, persons with disabilities and older persons</t>
+  </si>
+  <si>
+    <t>11.3.1</t>
+  </si>
+  <si>
+    <t>Ratio of land consumption rate to population growth rate</t>
+  </si>
+  <si>
+    <t>11.3</t>
+  </si>
+  <si>
+    <t>By 2030, enhance inclusive and sustainable urbanization and capacity for participatory, integrated and sustainable human settlement planning and management in all countries</t>
+  </si>
+  <si>
+    <t>11.3.2</t>
+  </si>
+  <si>
+    <t>Proportion of cities with a direct participation structure of civil society in urban planning and management that operate regularly and democratically</t>
+  </si>
+  <si>
+    <t>11.4.1</t>
+  </si>
+  <si>
+    <t>Total per capita expenditure on the preservation, protection and conservation of all cultural and natural heritage, by source of funding (public, private), type of heritage (cultural, natural) and level of government (national, regional, and local/municipal)</t>
+  </si>
+  <si>
+    <t>11.4</t>
+  </si>
+  <si>
+    <t>Strengthen efforts to protect and safeguard the world’s cultural and natural heritage</t>
+  </si>
+  <si>
+    <t>11.5.1</t>
+  </si>
+  <si>
+    <t>11.5</t>
+  </si>
+  <si>
+    <t>By 2030, significantly reduce the number of deaths and the number of people affected and substantially decrease the direct economic losses relative to global gross domestic product caused by disasters, including water-related disasters, with a focus on protecting the poor and people in vulnerable situations</t>
+  </si>
+  <si>
+    <t>11.5.2</t>
+  </si>
+  <si>
+    <t>Direct economic loss in relation to global GDP, damage to critical infrastructure and number of disruptions to basic services, attributed to disasters</t>
+  </si>
+  <si>
+    <t>11.6.1</t>
+  </si>
+  <si>
+    <t>Proportion of municipal solid waste collected and managed in controlled facilities out of total municipal waste generated, by cities</t>
+  </si>
+  <si>
+    <t>11.6</t>
+  </si>
+  <si>
+    <t>By 2030, reduce the adverse per capita environmental impact of cities, including by paying special attention to air quality and municipal and other waste management</t>
+  </si>
+  <si>
+    <t>11.6.2</t>
+  </si>
+  <si>
+    <t>Annual mean levels of fine particulate matter (e.g. PM2.5 and PM10) in cities (population weighted)</t>
+  </si>
+  <si>
+    <t>11.7.1</t>
+  </si>
+  <si>
+    <t>Average share of the built-up area of cities that is open space for public use for all, by sex, age and persons with disabilities</t>
+  </si>
+  <si>
+    <t>11.7</t>
+  </si>
+  <si>
+    <t>By 2030, provide universal access to safe, inclusive and accessible, green and public spaces, in particular for women and children, older persons and persons with disabilities</t>
+  </si>
+  <si>
+    <t>11.7.2</t>
+  </si>
+  <si>
+    <t>Proportion of persons victim of physical or sexual harassment, by sex, age, disability status and place of occurrence, in the previous 12 months</t>
+  </si>
+  <si>
+    <t>11.a.1</t>
+  </si>
+  <si>
+    <t>Number of countries that have national urban policies or regional development plans that (a) respond to population dynamics; (b) ensure balanced territorial development; and (c) increase local fiscal space</t>
+  </si>
+  <si>
+    <t>11.a</t>
+  </si>
+  <si>
+    <t>Support positive economic, social and environmental links between urban, peri-urban and rural areas by strengthening national and regional development planning</t>
+  </si>
+  <si>
+    <t>11.b.1</t>
+  </si>
+  <si>
+    <t>11.b</t>
+  </si>
+  <si>
+    <t>By 2020, substantially increase the number of cities and human settlements adopting and implementing integrated policies and plans towards inclusion, resource efficiency, mitigation and adaptation to climate change, resilience to disasters, and develop and implement, in line with the Sendai Framework for Disaster Risk Reduction 2015–2030, holistic disaster risk management at all levels</t>
+  </si>
+  <si>
+    <t>11.b.2</t>
+  </si>
+  <si>
+    <t>12.1.1</t>
+  </si>
+  <si>
+    <t>Number of countries developing, adopting or implementing policy instruments aimed at supporting the shift to sustainable consumption and production</t>
+  </si>
+  <si>
+    <t>12.1</t>
+  </si>
+  <si>
+    <t>Implement the 10‑Year Framework of Programmes on Sustainable Consumption and Production Patterns, all countries taking action, with developed countries taking the lead, taking into account the development and capabilities of developing countries</t>
+  </si>
+  <si>
+    <t>12.2.1</t>
+  </si>
+  <si>
+    <t>12.2</t>
+  </si>
+  <si>
+    <t>By 2030, achieve the sustainable management and efficient use of natural resources</t>
+  </si>
+  <si>
+    <t>12.2.2</t>
+  </si>
+  <si>
+    <t>12.3.1</t>
+  </si>
+  <si>
+    <t>(a) Food loss index and (b) food waste index</t>
+  </si>
+  <si>
+    <t>12.3</t>
+  </si>
+  <si>
+    <t>By 2030, halve per capita global food waste at the retail and consumer levels and reduce food losses along production and supply chains, including post-harvest losses</t>
+  </si>
+  <si>
+    <t>12.4.1</t>
+  </si>
+  <si>
+    <t>Number of parties to international multilateral environmental agreements on hazardous waste, and other chemicals that meet their commitments and obligations in transmitting information as required by each relevant agreement</t>
+  </si>
+  <si>
+    <t>12.4</t>
+  </si>
+  <si>
+    <t>By 2020, achieve the environmentally sound management of chemicals and all wastes throughout their life cycle, in accordance with agreed international frameworks, and significantly reduce their release to air, water and soil in order to minimize their adverse impacts on human health and the environment</t>
+  </si>
+  <si>
+    <t>12.4.2</t>
+  </si>
+  <si>
+    <t>(a) Hazardous waste generated per capita; and (b) proportion of hazardous waste treated, by type of treatment</t>
+  </si>
+  <si>
+    <t>12.5.1</t>
+  </si>
+  <si>
+    <t>National recycling rate, tons of material recycled</t>
+  </si>
+  <si>
+    <t>12.5</t>
+  </si>
+  <si>
+    <t>By 2030, substantially reduce waste generation through prevention, reduction, recycling and reuse</t>
+  </si>
+  <si>
+    <t>12.6.1</t>
+  </si>
+  <si>
+    <t>Number of companies publishing sustainability reports</t>
+  </si>
+  <si>
+    <t>12.6</t>
+  </si>
+  <si>
+    <t>Encourage companies, especially large and transnational companies, to adopt sustainable practices and to integrate sustainability information into their reporting cycle</t>
+  </si>
+  <si>
+    <t>12.7.1</t>
+  </si>
+  <si>
+    <t>Degree of sustainable public procurement policies and action plan implementation</t>
+  </si>
+  <si>
+    <t>12.7</t>
+  </si>
+  <si>
+    <t>Promote public procurement practices that are sustainable, in accordance with national policies and priorities</t>
+  </si>
+  <si>
+    <t>12.8.1</t>
+  </si>
+  <si>
+    <t>12.8</t>
+  </si>
+  <si>
+    <t>By 2030, ensure that people everywhere have the relevant information and awareness for sustainable development and lifestyles in harmony with nature</t>
+  </si>
+  <si>
+    <t>12.a.1</t>
+  </si>
+  <si>
+    <t>12.a</t>
+  </si>
+  <si>
+    <t>Support developing countries to strengthen their scientific and technological capacity to move towards more sustainable patterns of consumption and production</t>
+  </si>
+  <si>
+    <t>12.b.1</t>
+  </si>
+  <si>
+    <t>Implementation of standard accounting tools to monitor the economic and environmental aspects of tourism sustainability</t>
+  </si>
+  <si>
+    <t>12.b</t>
+  </si>
+  <si>
+    <t>Develop and implement tools to monitor sustainable development impacts for sustainable tourism that creates jobs and promotes local culture and products</t>
+  </si>
+  <si>
+    <t>12.c.1</t>
+  </si>
+  <si>
+    <t>Amount of fossil-fuel subsidies (production and consumption) per unit of GDP</t>
+  </si>
+  <si>
+    <t>12.c</t>
+  </si>
+  <si>
+    <t>Rationalize inefficient fossil-fuel subsidies that encourage wasteful consumption by removing market distortions, in accordance with national circumstances, including by restructuring taxation and phasing out those harmful subsidies, where they exist, to reflect their environmental impacts, taking fully into account the specific needs and conditions of developing countries and minimizing the possible adverse impacts on their development in a manner that protects the poor and the affected communities</t>
+  </si>
+  <si>
+    <t>13.1.1</t>
+  </si>
+  <si>
+    <t>13.1</t>
+  </si>
+  <si>
+    <t>Strengthen resilience and adaptive capacity to climate-related hazards and natural disasters in all countries</t>
+  </si>
+  <si>
+    <t>13.1.2</t>
+  </si>
+  <si>
+    <t>13.1.3</t>
+  </si>
+  <si>
+    <t>13.2.1</t>
+  </si>
+  <si>
+    <t>Number of countries with nationally determined contributions, long-term strategies, national adaptation plans and adaptation communications, as reported to the secretariat of the United Nations Framework Convention on Climate Change</t>
+  </si>
+  <si>
+    <t>13.2</t>
+  </si>
+  <si>
+    <t>Integrate climate change measures into national policies, strategies and planning</t>
+  </si>
+  <si>
+    <t>13.2.2</t>
+  </si>
+  <si>
+    <t>Total greenhouse gas emissions per year</t>
+  </si>
+  <si>
+    <t>13.3.1</t>
+  </si>
+  <si>
+    <t>13.3</t>
+  </si>
+  <si>
+    <t>Improve education, awareness-raising and human and institutional capacity on climate change mitigation, adaptation, impact reduction and early warning</t>
+  </si>
+  <si>
+    <t>13.a.1</t>
+  </si>
+  <si>
+    <t>Amounts provided and mobilized in United States dollars per year in relation to the continued existing collective mobilization goal of the $100 billion commitment through to 2025</t>
+  </si>
+  <si>
+    <t>13.a</t>
+  </si>
+  <si>
+    <t>Implement the commitment undertaken by developed-country parties to the United Nations Framework Convention on Climate Change to a goal of mobilizing jointly $100 billion annually by 2020 from all sources to address the needs of developing countries in the context of meaningful mitigation actions and transparency on implementation and fully operationalize the Green Climate Fund through its capitalization as soon as possible</t>
+  </si>
+  <si>
+    <t>13.b.1</t>
+  </si>
+  <si>
+    <t>Number of least developed countries and small island developing States with nationally determined contributions, long-term strategies, national adaptation plans and adaptation communications, as reported to the secretariat of the United Nations Framework Convention on Climate Change</t>
+  </si>
+  <si>
+    <t>13.b</t>
+  </si>
+  <si>
+    <t>Promote mechanisms for raising capacity for effective climate change-related planning and management in least developed countries and small island developing States, including focusing on women, youth and local and marginalized communities</t>
+  </si>
+  <si>
+    <t>14.1.1</t>
+  </si>
+  <si>
+    <t>(a) Index of coastal eutrophication; and (b) plastic debris density</t>
+  </si>
+  <si>
+    <t>14.1</t>
+  </si>
+  <si>
+    <t>By 2025, prevent and significantly reduce marine pollution of all kinds, in particular from land-based activities, including marine debris and nutrient pollution</t>
+  </si>
+  <si>
+    <t>14.2.1</t>
+  </si>
+  <si>
+    <t>Number of countries using ecosystem-based approaches to managing marine areas</t>
+  </si>
+  <si>
+    <t>14.2</t>
+  </si>
+  <si>
+    <t>By 2020, sustainably manage and protect marine and coastal ecosystems to avoid significant adverse impacts, including by strengthening their resilience, and take action for their restoration in order to achieve healthy and productive oceans</t>
+  </si>
+  <si>
+    <t>14.3.1</t>
+  </si>
+  <si>
+    <t>Average marine acidity (pH) measured at agreed suite of representative sampling stations</t>
+  </si>
+  <si>
+    <t>14.3</t>
+  </si>
+  <si>
+    <t>Minimize and address the impacts of ocean acidification, including through enhanced scientific cooperation at all levels</t>
+  </si>
+  <si>
+    <t>14.4.1</t>
+  </si>
+  <si>
+    <t>Proportion of fish stocks within biologically sustainable levels</t>
+  </si>
+  <si>
+    <t>14.4</t>
+  </si>
+  <si>
+    <t>By 2020, effectively regulate harvesting and end overfishing, illegal, unreported and unregulated fishing and destructive fishing practices and implement science-based management plans, in order to restore fish stocks in the shortest time feasible, at least to levels that can produce maximum sustainable yield as determined by their biological characteristics</t>
+  </si>
+  <si>
+    <t>14.5.1</t>
+  </si>
+  <si>
+    <t>Coverage of protected areas in relation to marine areas</t>
+  </si>
+  <si>
+    <t>14.5</t>
+  </si>
+  <si>
+    <t>By 2020, conserve at least 10 per cent of coastal and marine areas, consistent with national and international law and based on the best available scientific information</t>
+  </si>
+  <si>
+    <t>14.6.1</t>
+  </si>
+  <si>
+    <t>Degree of implementation of international instruments aiming to combat illegal, unreported and unregulated fishing</t>
+  </si>
+  <si>
+    <t>14.6</t>
+  </si>
+  <si>
+    <t>By 2020, prohibit certain forms of fisheries subsidies which contribute to overcapacity and overfishing, eliminate subsidies that contribute to illegal, unreported and unregulated fishing and refrain from introducing new such subsidies, recognizing that appropriate and effective special and differential treatment for developing and least developed countries should be an integral part of the World Trade Organization fisheries subsidies negotiation3</t>
+  </si>
+  <si>
+    <t>14.7.1</t>
+  </si>
+  <si>
+    <t>Sustainable fisheries as a proportion of GDP in small island developing States, least developed countries and all countries</t>
+  </si>
+  <si>
+    <t>14.7</t>
+  </si>
+  <si>
+    <t>By 2030, increase the economic benefits to small island developing States and least developed countries from the sustainable use of marine resources, including through sustainable management of fisheries, aquaculture and tourism</t>
+  </si>
+  <si>
+    <t>14.a.1</t>
+  </si>
+  <si>
+    <t>Proportion of total research budget allocated to research in the field of marine technology</t>
+  </si>
+  <si>
+    <t>14.a</t>
+  </si>
+  <si>
+    <t>Increase scientific knowledge, develop research capacity and transfer marine technology, taking into account the Intergovernmental Oceanographic Commission Criteria and Guidelines on the Transfer of Marine Technology, in order to improve ocean health and to enhance the contribution of marine biodiversity to the development of developing countries, in particular small island developing States and least developed countries</t>
+  </si>
+  <si>
+    <t>14.b.1</t>
+  </si>
+  <si>
+    <t>Degree of application of a legal/regulatory/ policy/institutional framework which recognizes and protects access rights for small-scale fisheries</t>
+  </si>
+  <si>
+    <t>14.b</t>
+  </si>
+  <si>
+    <t>Provide access for small-scale artisanal fishers to marine resources and markets</t>
+  </si>
+  <si>
+    <t>14.c.1</t>
+  </si>
+  <si>
+    <t>Number of countries making progress in ratifying, accepting and implementing through legal, policy and institutional frameworks, ocean-related instruments that implement international law, as reflected in the United Nations Convention on the Law of the Sea, for the conservation and sustainable use of the oceans and their resources</t>
+  </si>
+  <si>
+    <t>14.c</t>
+  </si>
+  <si>
+    <t>Enhance the conservation and sustainable use of oceans and their resources by implementing international law as reflected in the United Nations Convention on the Law of the Sea, which provides the legal framework for the conservation and sustainable use of oceans and their resources, as recalled in paragraph 158 of “The future we want”</t>
+  </si>
+  <si>
+    <t>15.1.1</t>
+  </si>
+  <si>
+    <t>Forest area as a proportion of total land area</t>
+  </si>
+  <si>
+    <t>15.1</t>
+  </si>
+  <si>
+    <t>By 2020, ensure the conservation, restoration and sustainable use of terrestrial and inland freshwater ecosystems and their services, in particular forests, wetlands, mountains and drylands, in line with obligations under international agreements</t>
+  </si>
+  <si>
+    <t>15.1.2</t>
+  </si>
+  <si>
+    <t>Proportion of important sites for terrestrial and freshwater biodiversity that are covered by protected areas, by ecosystem type</t>
+  </si>
+  <si>
+    <t>15.2.1</t>
+  </si>
+  <si>
+    <t>Progress towards sustainable forest management</t>
+  </si>
+  <si>
+    <t>15.2</t>
+  </si>
+  <si>
+    <t>By 2020, promote the implementation of sustainable management of all types of forests, halt deforestation, restore degraded forests and substantially increase afforestation and reforestation globally</t>
+  </si>
+  <si>
+    <t>15.3.1</t>
+  </si>
+  <si>
+    <t>Proportion of land that is degraded over total land area</t>
+  </si>
+  <si>
+    <t>15.3</t>
+  </si>
+  <si>
+    <t>By 2030, combat desertification, restore degraded land and soil, including land affected by desertification, drought and floods, and strive to achieve a land degradation-neutral world</t>
+  </si>
+  <si>
+    <t>15.4.1</t>
+  </si>
+  <si>
+    <t>Coverage by protected areas of important sites for mountain biodiversity</t>
+  </si>
+  <si>
+    <t>15.4</t>
+  </si>
+  <si>
+    <t>By 2030, ensure the conservation of mountain ecosystems, including their biodiversity, in order to enhance their capacity to provide benefits that are essential for sustainable development</t>
+  </si>
+  <si>
+    <t>15.4.2</t>
+  </si>
+  <si>
+    <t>Mountain Green Cover Index</t>
+  </si>
+  <si>
+    <t>15.5.1</t>
+  </si>
+  <si>
+    <t>Red List Index</t>
+  </si>
+  <si>
+    <t>15.5</t>
+  </si>
+  <si>
+    <t>Take urgent and significant action to reduce the degradation of natural habitats, halt the loss of biodiversity and, by 2020, protect and prevent the extinction of threatened species</t>
+  </si>
+  <si>
+    <t>15.6.1</t>
+  </si>
+  <si>
+    <t>Number of countries that have adopted legislative, administrative and policy frameworks to ensure fair and equitable sharing of benefits</t>
+  </si>
+  <si>
+    <t>15.6</t>
+  </si>
+  <si>
+    <t>Promote fair and equitable sharing of the benefits arising from the utilization of genetic resources and promote appropriate access to such resources, as internationally agreed</t>
+  </si>
+  <si>
+    <t>15.7.1</t>
+  </si>
+  <si>
+    <t>Proportion of traded wildlife that was poached or illicitly trafficked</t>
+  </si>
+  <si>
+    <t>15.7</t>
+  </si>
+  <si>
+    <t>Take urgent action to end poaching and trafficking of protected species of flora and fauna and address both demand and supply of illegal wildlife products</t>
+  </si>
+  <si>
+    <t>15.8.1</t>
+  </si>
+  <si>
+    <t>Proportion of countries adopting relevant national legislation and adequately resourcing the prevention or control of invasive alien species</t>
+  </si>
+  <si>
+    <t>15.8</t>
+  </si>
+  <si>
+    <t>By 2020, introduce measures to prevent the introduction and significantly reduce the impact of invasive alien species on land and water ecosystems and control or eradicate the priority species</t>
+  </si>
+  <si>
+    <t>15.9.1</t>
+  </si>
+  <si>
+    <t>(a) Number of countries that have established national targets in accordance with or similar to Aichi Biodiversity Target 2 of the Strategic Plan for Biodiversity 2011–2020 in their national biodiversity strategy and action plans and the progress reported towards these targets; and (b) integration of biodiversity into national accounting and reporting systems, defined as implementation of the System of Environmental-Economic Accounting</t>
+  </si>
+  <si>
+    <t>15.9</t>
+  </si>
+  <si>
+    <t>By 2020, integrate ecosystem and biodiversity values into national and local planning, development processes, poverty reduction strategies and accounts</t>
+  </si>
+  <si>
+    <t>15.a.1</t>
+  </si>
+  <si>
+    <t>(a) Official development assistance on conservation and sustainable use of biodiversity; and (b) revenue generated and finance mobilized from biodiversity-relevant economic instruments</t>
+  </si>
+  <si>
+    <t>15.a</t>
+  </si>
+  <si>
+    <t>Mobilize and significantly increase financial resources from all sources to conserve and sustainably use biodiversity and ecosystems</t>
+  </si>
+  <si>
+    <t>15.b.1</t>
+  </si>
+  <si>
+    <t>15.b</t>
+  </si>
+  <si>
+    <t>Mobilize significant resources from all sources and at all levels to finance sustainable forest management and provide adequate incentives to developing countries to advance such management, including for conservation and reforestation</t>
+  </si>
+  <si>
+    <t>15.c.1</t>
+  </si>
+  <si>
+    <t>15.c</t>
+  </si>
+  <si>
+    <t>Enhance global support for efforts to combat poaching and trafficking of protected species, including by increasing the capacity of local communities to pursue sustainable livelihood opportunities</t>
+  </si>
+  <si>
+    <t>16.1.1</t>
+  </si>
+  <si>
+    <t>Number of victims of intentional homicide per 100,000 population, by sex and age</t>
+  </si>
+  <si>
+    <t>16.1</t>
+  </si>
+  <si>
+    <t>Significantly reduce all forms of violence and related death rates everywhere</t>
+  </si>
+  <si>
+    <t>16.1.2</t>
+  </si>
+  <si>
+    <t>Conflict-related deaths per 100,000 population, by sex, age and cause</t>
+  </si>
+  <si>
+    <t>16.1.3</t>
+  </si>
+  <si>
+    <t>Proportion of population subjected to (a) physical violence, (b) psychological violence and (c) sexual violence in the previous 12 months</t>
+  </si>
+  <si>
+    <t>16.1.4</t>
+  </si>
+  <si>
+    <t>Proportion of population that feel safe walking alone around the area they live</t>
+  </si>
+  <si>
+    <t>16.2.1</t>
+  </si>
+  <si>
+    <t>Proportion of children aged 1–17 years who experienced any physical punishment and/or psychological aggression by caregivers in the past month</t>
+  </si>
+  <si>
+    <t>16.2</t>
+  </si>
+  <si>
+    <t>End abuse, exploitation, trafficking and all forms of violence against and torture of children</t>
+  </si>
+  <si>
+    <t>16.2.2</t>
+  </si>
+  <si>
+    <t>Number of victims of human trafficking per 100,000 population, by sex, age and form of exploitation</t>
+  </si>
+  <si>
+    <t>16.2.3</t>
+  </si>
+  <si>
+    <t>Proportion of young women and men aged 18–29 years who experienced sexual violence by age 18</t>
+  </si>
+  <si>
+    <t>16.3.1</t>
+  </si>
+  <si>
+    <t>Proportion of victims of violence in the previous 12 months who reported their victimization to competent authorities or other officially recognized conflict resolution mechanisms</t>
+  </si>
+  <si>
+    <t>16.3</t>
+  </si>
+  <si>
+    <t>Promote the rule of law at the national and international levels and ensure equal access to justice for all</t>
+  </si>
+  <si>
+    <t>16.3.2</t>
+  </si>
+  <si>
+    <t>Unsentenced detainees as a proportion of overall prison population</t>
+  </si>
+  <si>
+    <t>16.3.3</t>
+  </si>
+  <si>
+    <t>Proportion of the population who have experienced a dispute in the past two years and who accessed a formal or informal dispute resolution mechanism, by type of mechanism</t>
+  </si>
+  <si>
+    <t>16.4.1</t>
+  </si>
+  <si>
+    <t>Total value of inward and outward illicit financial flows (in current United States dollars)</t>
+  </si>
+  <si>
+    <t>16.4</t>
+  </si>
+  <si>
+    <t>By 2030, significantly reduce illicit financial and arms flows, strengthen the recovery and return of stolen assets and combat all forms of organized crime</t>
+  </si>
+  <si>
+    <t>16.4.2</t>
+  </si>
+  <si>
+    <t>Proportion of seized, found or surrendered arms whose illicit origin or context has been traced or established by a competent authority in line with international instruments</t>
+  </si>
+  <si>
+    <t>16.5.1</t>
+  </si>
+  <si>
+    <t>Proportion of persons who had at least one contact with a public official and who paid a bribe to a public official, or were asked for a bribe by those public officials, during the previous 12 months</t>
+  </si>
+  <si>
+    <t>16.5</t>
+  </si>
+  <si>
+    <t>Substantially reduce corruption and bribery in all their forms</t>
+  </si>
+  <si>
+    <t>16.5.2</t>
+  </si>
+  <si>
+    <t>Proportion of businesses that had at least one contact with a public official and that paid a bribe to a public official, or were asked for a bribe by those public officials during the previous 12 months</t>
+  </si>
+  <si>
+    <t>16.6.1</t>
+  </si>
+  <si>
+    <t>Primary government expenditures as a proportion of original approved budget, by sector (or by budget codes or similar)</t>
+  </si>
+  <si>
+    <t>16.6</t>
+  </si>
+  <si>
+    <t>Develop effective, accountable and transparent institutions at all levels</t>
+  </si>
+  <si>
+    <t>16.6.2</t>
+  </si>
+  <si>
+    <t>Proportion of population satisfied with their last experience of public services</t>
+  </si>
+  <si>
+    <t>16.7.1</t>
+  </si>
+  <si>
+    <t>Proportions of positions in national and local institutions, including (a) the legislatures; (b) the public service; and (c) the judiciary, compared to national distributions, by sex, age, persons with disabilities and population groups</t>
+  </si>
+  <si>
+    <t>16.7</t>
+  </si>
+  <si>
+    <t>Ensure responsive, inclusive, participatory and representative decision-making at all levels</t>
+  </si>
+  <si>
+    <t>16.7.2</t>
+  </si>
+  <si>
+    <t>Proportion of population who believe decision-making is inclusive and responsive, by sex, age, disability and population group</t>
+  </si>
+  <si>
+    <t>16.8.1</t>
+  </si>
+  <si>
+    <t>16.8</t>
+  </si>
+  <si>
+    <t>Broaden and strengthen the participation of developing countries in the institutions of global governance</t>
+  </si>
+  <si>
+    <t>16.9.1</t>
+  </si>
+  <si>
+    <t>Proportion of children under 5 years of age whose births have been registered with a civil authority, by age</t>
+  </si>
+  <si>
+    <t>16.9</t>
+  </si>
+  <si>
+    <t>By 2030, provide legal identity for all, including birth registration</t>
+  </si>
+  <si>
+    <t>16.10.1</t>
+  </si>
+  <si>
+    <t>Number of verified cases of killing, kidnapping, enforced disappearance, arbitrary detention and torture of journalists, associated media personnel, trade unionists and human rights advocates in the previous 12 months</t>
+  </si>
+  <si>
+    <t>16.10</t>
+  </si>
+  <si>
+    <t>Ensure public access to information and protect fundamental freedoms, in accordance with national legislation and international agreements</t>
+  </si>
+  <si>
+    <t>16.10.2</t>
+  </si>
+  <si>
+    <t>Number of countries that adopt and implement constitutional, statutory and/or policy guarantees for public access to information</t>
+  </si>
+  <si>
+    <t>16.a.1</t>
+  </si>
+  <si>
+    <t>Existence of independent national human rights institutions in compliance with the Paris Principles</t>
+  </si>
+  <si>
+    <t>16.a</t>
+  </si>
+  <si>
+    <t>Strengthen relevant national institutions, including through international cooperation, for building capacity at all levels, in particular in developing countries, to prevent violence and combat terrorism and crime</t>
+  </si>
+  <si>
+    <t>16.b.1</t>
+  </si>
+  <si>
     <t>Proportion of population reporting having personally felt discriminated against or harassed in the previous 12 months on the basis of a ground of discrimination prohibited under international human rights law</t>
   </si>
   <si>
-    <t>10.3</t>
-  </si>
-  <si>
-    <t>Ensure equal opportunity and reduce inequalities of outcome, including by eliminating discriminatory laws, policies and practices and promoting appropriate legislation, policies and action in this regard</t>
-  </si>
-  <si>
-    <t>10.4.1</t>
-  </si>
-  <si>
-    <t>Labour share of GDP</t>
-  </si>
-  <si>
-    <t>10.4</t>
-  </si>
-  <si>
-    <t>Adopt policies, especially fiscal, wage and social protection policies, and progressively achieve greater equality</t>
-  </si>
-  <si>
-    <t>10.4.2</t>
-  </si>
-  <si>
-    <t>Redistributive impact of fiscal policy</t>
-  </si>
-  <si>
-    <t>10.5.1</t>
-  </si>
-  <si>
-    <t>Financial Soundness Indicators</t>
-  </si>
-  <si>
-    <t>10.5</t>
-  </si>
-  <si>
-    <t>Improve the regulation and monitoring of global financial markets and institutions and strengthen the implementation of such regulations</t>
-  </si>
-  <si>
-    <t>10.6.1</t>
-  </si>
-  <si>
-    <t>Proportion of members and voting rights of developing countries in international organizations</t>
-  </si>
-  <si>
-    <t>10.6</t>
-  </si>
-  <si>
-    <t>Ensure enhanced representation and voice for developing countries in decision-making in global international economic and financial institutions in order to deliver more effective, credible, accountable and legitimate institutions</t>
-  </si>
-  <si>
-    <t>10.7.1</t>
-  </si>
-  <si>
-    <t>Recruitment cost borne by employee as a proportion of monthly income earned in country of destination</t>
-  </si>
-  <si>
-    <t>10.7</t>
-  </si>
-  <si>
-    <t>Facilitate orderly, safe, regular and responsible migration and mobility of people, including through the implementation of planned and well-managed migration policies</t>
-  </si>
-  <si>
-    <t>10.7.2</t>
-  </si>
-  <si>
-    <t>Number of countries with migration policies that facilitate orderly, safe, regular and responsible migration and mobility of people</t>
-  </si>
-  <si>
-    <t>10.7.3</t>
-  </si>
-  <si>
-    <t>Number of people who died or disappeared in the process of migration towards an international destination</t>
-  </si>
-  <si>
-    <t>10.7.4</t>
-  </si>
-  <si>
-    <t>Proportion of the population who are refugees, by country of origin</t>
-  </si>
-  <si>
-    <t>10.a.1</t>
-  </si>
-  <si>
-    <t>Proportion of tariff lines applied to imports from least developed countries and developing countries with zero-tariff</t>
-  </si>
-  <si>
-    <t>10.a</t>
-  </si>
-  <si>
-    <t>Implement the principle of special and differential treatment for developing countries, in particular least developed countries, in accordance with World Trade Organization agreements</t>
-  </si>
-  <si>
-    <t>10.b.1</t>
-  </si>
-  <si>
-    <t>Total resource flows for development, by recipient and donor countries and type of flow (e.g. official development assistance, foreign direct investment and other flows)</t>
-  </si>
-  <si>
-    <t>10.b</t>
-  </si>
-  <si>
-    <t>Encourage official development assistance and financial flows, including foreign direct investment, to States where the need is greatest, in particular least developed countries, African countries, small island developing States and landlocked developing countries, in accordance with their national plans and programmes</t>
-  </si>
-  <si>
-    <t>10.c.1</t>
-  </si>
-  <si>
-    <t>Remittance costs as a proportion of the amount remitted</t>
-  </si>
-  <si>
-    <t>10.c</t>
-  </si>
-  <si>
-    <t>By 2030, reduce to less than 3 per cent the transaction costs of migrant remittances and eliminate remittance corridors with costs higher than 5 per cent</t>
-  </si>
-  <si>
-    <t>11.1.1</t>
-  </si>
-  <si>
-    <t>Proportion of urban population living in slums, informal settlements or inadequate housing</t>
-  </si>
-  <si>
-    <t>11.1</t>
-  </si>
-  <si>
-    <t>By 2030, ensure access for all to adequate, safe and affordable housing and basic services and upgrade slums</t>
-  </si>
-  <si>
-    <t>11.2.1</t>
-  </si>
-  <si>
-    <t>Proportion of population that has convenient access to public transport, by sex, age and persons with disabilities</t>
-  </si>
-  <si>
-    <t>11.2</t>
-  </si>
-  <si>
-    <t>By 2030, provide access to safe, affordable, accessible and sustainable transport systems for all, improving road safety, notably by expanding public transport, with special attention to the needs of those in vulnerable situations, women, children, persons with disabilities and older persons</t>
-  </si>
-  <si>
-    <t>11.3.1</t>
-  </si>
-  <si>
-    <t>Ratio of land consumption rate to population growth rate</t>
-  </si>
-  <si>
-    <t>11.3</t>
-  </si>
-  <si>
-    <t>By 2030, enhance inclusive and sustainable urbanization and capacity for participatory, integrated and sustainable human settlement planning and management in all countries</t>
-  </si>
-  <si>
-    <t>11.3.2</t>
-  </si>
-  <si>
-    <t>Proportion of cities with a direct participation structure of civil society in urban planning and management that operate regularly and democratically</t>
-  </si>
-  <si>
-    <t>11.4.1</t>
-  </si>
-  <si>
-    <t>Total per capita expenditure on the preservation, protection and conservation of all cultural and natural heritage, by source of funding (public, private), type of heritage (cultural, natural) and level of government (national, regional, and local/municipal)</t>
-  </si>
-  <si>
-    <t>11.4</t>
-  </si>
-  <si>
-    <t>Strengthen efforts to protect and safeguard the world’s cultural and natural heritage</t>
-  </si>
-  <si>
-    <t>11.5.1</t>
-  </si>
-  <si>
-    <t>11.5</t>
-  </si>
-  <si>
-    <t>By 2030, significantly reduce the number of deaths and the number of people affected and substantially decrease the direct economic losses relative to global gross domestic product caused by disasters, including water-related disasters, with a focus on protecting the poor and people in vulnerable situations</t>
-  </si>
-  <si>
-    <t>11.5.2</t>
-  </si>
-  <si>
-    <t>Direct economic loss in relation to global GDP, damage to critical infrastructure and number of disruptions to basic services, attributed to disasters</t>
-  </si>
-  <si>
-    <t>11.6.1</t>
-  </si>
-  <si>
-    <t>Proportion of municipal solid waste collected and managed in controlled facilities out of total municipal waste generated, by cities</t>
-  </si>
-  <si>
-    <t>11.6</t>
-  </si>
-  <si>
-    <t>By 2030, reduce the adverse per capita environmental impact of cities, including by paying special attention to air quality and municipal and other waste management</t>
-  </si>
-  <si>
-    <t>11.6.2</t>
-  </si>
-  <si>
-    <t>Annual mean levels of fine particulate matter (e.g. PM2.5 and PM10) in cities (population weighted)</t>
-  </si>
-  <si>
-    <t>11.7.1</t>
-  </si>
-  <si>
-    <t>Average share of the built-up area of cities that is open space for public use for all, by sex, age and persons with disabilities</t>
-  </si>
-  <si>
-    <t>11.7</t>
-  </si>
-  <si>
-    <t>By 2030, provide universal access to safe, inclusive and accessible, green and public spaces, in particular for women and children, older persons and persons with disabilities</t>
-  </si>
-  <si>
-    <t>11.7.2</t>
-  </si>
-  <si>
-    <t>Proportion of persons victim of physical or sexual harassment, by sex, age, disability status and place of occurrence, in the previous 12 months</t>
-  </si>
-  <si>
-    <t>11.a.1</t>
-  </si>
-  <si>
-    <t>Number of countries that have national urban policies or regional development plans that (a) respond to population dynamics; (b) ensure balanced territorial development; and (c) increase local fiscal space</t>
-  </si>
-  <si>
-    <t>11.a</t>
-  </si>
-  <si>
-    <t>Support positive economic, social and environmental links between urban, peri-urban and rural areas by strengthening national and regional development planning</t>
-  </si>
-  <si>
-    <t>11.b.1</t>
-  </si>
-  <si>
-    <t>11.b</t>
-  </si>
-  <si>
-    <t>By 2020, substantially increase the number of cities and human settlements adopting and implementing integrated policies and plans towards inclusion, resource efficiency, mitigation and adaptation to climate change, resilience to disasters, and develop and implement, in line with the Sendai Framework for Disaster Risk Reduction 2015–2030, holistic disaster risk management at all levels</t>
-  </si>
-  <si>
-    <t>11.b.2</t>
-  </si>
-  <si>
-    <t>12.1.1</t>
-  </si>
-  <si>
-    <t>Number of countries developing, adopting or implementing policy instruments aimed at supporting the shift to sustainable consumption and production</t>
-  </si>
-  <si>
-    <t>12.1</t>
-  </si>
-  <si>
-    <t>Implement the 10‑Year Framework of Programmes on Sustainable Consumption and Production Patterns, all countries taking action, with developed countries taking the lead, taking into account the development and capabilities of developing countries</t>
-  </si>
-  <si>
-    <t>12.2.1</t>
-  </si>
-  <si>
-    <t>12.2</t>
-  </si>
-  <si>
-    <t>By 2030, achieve the sustainable management and efficient use of natural resources</t>
-  </si>
-  <si>
-    <t>12.2.2</t>
-  </si>
-  <si>
-    <t>12.3.1</t>
-  </si>
-  <si>
-    <t>(a) Food loss index and (b) food waste index</t>
-  </si>
-  <si>
-    <t>12.3</t>
-  </si>
-  <si>
-    <t>By 2030, halve per capita global food waste at the retail and consumer levels and reduce food losses along production and supply chains, including post-harvest losses</t>
-  </si>
-  <si>
-    <t>12.4.1</t>
-  </si>
-  <si>
-    <t>Number of parties to international multilateral environmental agreements on hazardous waste, and other chemicals that meet their commitments and obligations in transmitting information as required by each relevant agreement</t>
-  </si>
-  <si>
-    <t>12.4</t>
-  </si>
-  <si>
-    <t>By 2020, achieve the environmentally sound management of chemicals and all wastes throughout their life cycle, in accordance with agreed international frameworks, and significantly reduce their release to air, water and soil in order to minimize their adverse impacts on human health and the environment</t>
-  </si>
-  <si>
-    <t>12.4.2</t>
-  </si>
-  <si>
-    <t>(a) Hazardous waste generated per capita; and (b) proportion of hazardous waste treated, by type of treatment</t>
-  </si>
-  <si>
-    <t>12.5.1</t>
-  </si>
-  <si>
-    <t>National recycling rate, tons of material recycled</t>
-  </si>
-  <si>
-    <t>12.5</t>
-  </si>
-  <si>
-    <t>By 2030, substantially reduce waste generation through prevention, reduction, recycling and reuse</t>
-  </si>
-  <si>
-    <t>12.6.1</t>
-  </si>
-  <si>
-    <t>Number of companies publishing sustainability reports</t>
-  </si>
-  <si>
-    <t>12.6</t>
-  </si>
-  <si>
-    <t>Encourage companies, especially large and transnational companies, to adopt sustainable practices and to integrate sustainability information into their reporting cycle</t>
-  </si>
-  <si>
-    <t>12.7.1</t>
-  </si>
-  <si>
-    <t>Degree of sustainable public procurement policies and action plan implementation</t>
-  </si>
-  <si>
-    <t>12.7</t>
-  </si>
-  <si>
-    <t>Promote public procurement practices that are sustainable, in accordance with national policies and priorities</t>
-  </si>
-  <si>
-    <t>12.8.1</t>
-  </si>
-  <si>
-    <t>12.8</t>
-  </si>
-  <si>
-    <t>By 2030, ensure that people everywhere have the relevant information and awareness for sustainable development and lifestyles in harmony with nature</t>
-  </si>
-  <si>
-    <t>12.a.1</t>
-  </si>
-  <si>
-    <t>12.a</t>
-  </si>
-  <si>
-    <t>Support developing countries to strengthen their scientific and technological capacity to move towards more sustainable patterns of consumption and production</t>
-  </si>
-  <si>
-    <t>12.b.1</t>
-  </si>
-  <si>
-    <t>Implementation of standard accounting tools to monitor the economic and environmental aspects of tourism sustainability</t>
-  </si>
-  <si>
-    <t>12.b</t>
-  </si>
-  <si>
-    <t>Develop and implement tools to monitor sustainable development impacts for sustainable tourism that creates jobs and promotes local culture and products</t>
-  </si>
-  <si>
-    <t>12.c.1</t>
-  </si>
-  <si>
-    <t>Amount of fossil-fuel subsidies (production and consumption) per unit of GDP</t>
-  </si>
-  <si>
-    <t>12.c</t>
-  </si>
-  <si>
-    <t>Rationalize inefficient fossil-fuel subsidies that encourage wasteful consumption by removing market distortions, in accordance with national circumstances, including by restructuring taxation and phasing out those harmful subsidies, where they exist, to reflect their environmental impacts, taking fully into account the specific needs and conditions of developing countries and minimizing the possible adverse impacts on their development in a manner that protects the poor and the affected communities</t>
-  </si>
-  <si>
-    <t>13.1.1</t>
-  </si>
-  <si>
-    <t>13.1</t>
-  </si>
-  <si>
-    <t>Strengthen resilience and adaptive capacity to climate-related hazards and natural disasters in all countries</t>
-  </si>
-  <si>
-    <t>13.1.2</t>
-  </si>
-  <si>
-    <t>13.1.3</t>
-  </si>
-  <si>
-    <t>13.2.1</t>
-  </si>
-  <si>
-    <t>Number of countries with nationally determined contributions, long-term strategies, national adaptation plans and adaptation communications, as reported to the secretariat of the United Nations Framework Convention on Climate Change</t>
-  </si>
-  <si>
-    <t>13.2</t>
-  </si>
-  <si>
-    <t>Integrate climate change measures into national policies, strategies and planning</t>
-  </si>
-  <si>
-    <t>13.2.2</t>
-  </si>
-  <si>
-    <t>Total greenhouse gas emissions per year</t>
-  </si>
-  <si>
-    <t>13.3.1</t>
-  </si>
-  <si>
-    <t>13.3</t>
-  </si>
-  <si>
-    <t>Improve education, awareness-raising and human and institutional capacity on climate change mitigation, adaptation, impact reduction and early warning</t>
-  </si>
-  <si>
-    <t>13.a.1</t>
-  </si>
-  <si>
-    <t>Amounts provided and mobilized in United States dollars per year in relation to the continued existing collective mobilization goal of the $100 billion commitment through to 2025</t>
-  </si>
-  <si>
-    <t>13.a</t>
-  </si>
-  <si>
-    <t>Implement the commitment undertaken by developed-country parties to the United Nations Framework Convention on Climate Change to a goal of mobilizing jointly $100 billion annually by 2020 from all sources to address the needs of developing countries in the context of meaningful mitigation actions and transparency on implementation and fully operationalize the Green Climate Fund through its capitalization as soon as possible</t>
-  </si>
-  <si>
-    <t>13.b.1</t>
-  </si>
-  <si>
-    <t>Number of least developed countries and small island developing States with nationally determined contributions, long-term strategies, national adaptation plans and adaptation communications, as reported to the secretariat of the United Nations Framework Convention on Climate Change</t>
-  </si>
-  <si>
-    <t>13.b</t>
-  </si>
-  <si>
-    <t>Promote mechanisms for raising capacity for effective climate change-related planning and management in least developed countries and small island developing States, including focusing on women, youth and local and marginalized communities</t>
-  </si>
-  <si>
-    <t>14.1.1</t>
-  </si>
-  <si>
-    <t>(a) Index of coastal eutrophication; and (b) plastic debris density</t>
-  </si>
-  <si>
-    <t>14.1</t>
-  </si>
-  <si>
-    <t>By 2025, prevent and significantly reduce marine pollution of all kinds, in particular from land-based activities, including marine debris and nutrient pollution</t>
-  </si>
-  <si>
-    <t>14.2.1</t>
-  </si>
-  <si>
-    <t>Number of countries using ecosystem-based approaches to managing marine areas</t>
-  </si>
-  <si>
-    <t>14.2</t>
-  </si>
-  <si>
-    <t>By 2020, sustainably manage and protect marine and coastal ecosystems to avoid significant adverse impacts, including by strengthening their resilience, and take action for their restoration in order to achieve healthy and productive oceans</t>
-  </si>
-  <si>
-    <t>14.3.1</t>
-  </si>
-  <si>
-    <t>Average marine acidity (pH) measured at agreed suite of representative sampling stations</t>
-  </si>
-  <si>
-    <t>14.3</t>
-  </si>
-  <si>
-    <t>Minimize and address the impacts of ocean acidification, including through enhanced scientific cooperation at all levels</t>
-  </si>
-  <si>
-    <t>14.4.1</t>
-  </si>
-  <si>
-    <t>Proportion of fish stocks within biologically sustainable levels</t>
-  </si>
-  <si>
-    <t>14.4</t>
-  </si>
-  <si>
-    <t>By 2020, effectively regulate harvesting and end overfishing, illegal, unreported and unregulated fishing and destructive fishing practices and implement science-based management plans, in order to restore fish stocks in the shortest time feasible, at least to levels that can produce maximum sustainable yield as determined by their biological characteristics</t>
-  </si>
-  <si>
-    <t>14.5.1</t>
-  </si>
-  <si>
-    <t>Coverage of protected areas in relation to marine areas</t>
-  </si>
-  <si>
-    <t>14.5</t>
-  </si>
-  <si>
-    <t>By 2020, conserve at least 10 per cent of coastal and marine areas, consistent with national and international law and based on the best available scientific information</t>
-  </si>
-  <si>
-    <t>14.6.1</t>
-  </si>
-  <si>
-    <t>Degree of implementation of international instruments aiming to combat illegal, unreported and unregulated fishing</t>
-  </si>
-  <si>
-    <t>14.6</t>
-  </si>
-  <si>
-    <t>By 2020, prohibit certain forms of fisheries subsidies which contribute to overcapacity and overfishing, eliminate subsidies that contribute to illegal, unreported and unregulated fishing and refrain from introducing new such subsidies, recognizing that appropriate and effective special and differential treatment for developing and least developed countries should be an integral part of the World Trade Organization fisheries subsidies negotiation3</t>
-  </si>
-  <si>
-    <t>14.7.1</t>
-  </si>
-  <si>
-    <t>Sustainable fisheries as a proportion of GDP in small island developing States, least developed countries and all countries</t>
-  </si>
-  <si>
-    <t>14.7</t>
-  </si>
-  <si>
-    <t>By 2030, increase the economic benefits to small island developing States and least developed countries from the sustainable use of marine resources, including through sustainable management of fisheries, aquaculture and tourism</t>
-  </si>
-  <si>
-    <t>14.a.1</t>
-  </si>
-  <si>
-    <t>Proportion of total research budget allocated to research in the field of marine technology</t>
-  </si>
-  <si>
-    <t>14.a</t>
-  </si>
-  <si>
-    <t>Increase scientific knowledge, develop research capacity and transfer marine technology, taking into account the Intergovernmental Oceanographic Commission Criteria and Guidelines on the Transfer of Marine Technology, in order to improve ocean health and to enhance the contribution of marine biodiversity to the development of developing countries, in particular small island developing States and least developed countries</t>
-  </si>
-  <si>
-    <t>14.b.1</t>
-  </si>
-  <si>
-    <t>Degree of application of a legal/regulatory/ policy/institutional framework which recognizes and protects access rights for small-scale fisheries</t>
-  </si>
-  <si>
-    <t>14.b</t>
-  </si>
-  <si>
-    <t>Provide access for small-scale artisanal fishers to marine resources and markets</t>
-  </si>
-  <si>
-    <t>14.c.1</t>
-  </si>
-  <si>
-    <t>Number of countries making progress in ratifying, accepting and implementing through legal, policy and institutional frameworks, ocean-related instruments that implement international law, as reflected in the United Nations Convention on the Law of the Sea, for the conservation and sustainable use of the oceans and their resources</t>
-  </si>
-  <si>
-    <t>14.c</t>
-  </si>
-  <si>
-    <t>Enhance the conservation and sustainable use of oceans and their resources by implementing international law as reflected in the United Nations Convention on the Law of the Sea, which provides the legal framework for the conservation and sustainable use of oceans and their resources, as recalled in paragraph 158 of “The future we want”</t>
-  </si>
-  <si>
-    <t>15.1.1</t>
-  </si>
-  <si>
-    <t>Forest area as a proportion of total land area</t>
-  </si>
-  <si>
-    <t>15.1</t>
-  </si>
-  <si>
-    <t>By 2020, ensure the conservation, restoration and sustainable use of terrestrial and inland freshwater ecosystems and their services, in particular forests, wetlands, mountains and drylands, in line with obligations under international agreements</t>
-  </si>
-  <si>
-    <t>15.1.2</t>
-  </si>
-  <si>
-    <t>Proportion of important sites for terrestrial and freshwater biodiversity that are covered by protected areas, by ecosystem type</t>
-  </si>
-  <si>
-    <t>15.2.1</t>
-  </si>
-  <si>
-    <t>Progress towards sustainable forest management</t>
-  </si>
-  <si>
-    <t>15.2</t>
-  </si>
-  <si>
-    <t>By 2020, promote the implementation of sustainable management of all types of forests, halt deforestation, restore degraded forests and substantially increase afforestation and reforestation globally</t>
-  </si>
-  <si>
-    <t>15.3.1</t>
-  </si>
-  <si>
-    <t>Proportion of land that is degraded over total land area</t>
-  </si>
-  <si>
-    <t>15.3</t>
-  </si>
-  <si>
-    <t>By 2030, combat desertification, restore degraded land and soil, including land affected by desertification, drought and floods, and strive to achieve a land degradation-neutral world</t>
-  </si>
-  <si>
-    <t>15.4.1</t>
-  </si>
-  <si>
-    <t>Coverage by protected areas of important sites for mountain biodiversity</t>
-  </si>
-  <si>
-    <t>15.4</t>
-  </si>
-  <si>
-    <t>By 2030, ensure the conservation of mountain ecosystems, including their biodiversity, in order to enhance their capacity to provide benefits that are essential for sustainable development</t>
-  </si>
-  <si>
-    <t>15.4.2</t>
-  </si>
-  <si>
-    <t>Mountain Green Cover Index</t>
-  </si>
-  <si>
-    <t>15.5.1</t>
-  </si>
-  <si>
-    <t>Red List Index</t>
-  </si>
-  <si>
-    <t>15.5</t>
-  </si>
-  <si>
-    <t>Take urgent and significant action to reduce the degradation of natural habitats, halt the loss of biodiversity and, by 2020, protect and prevent the extinction of threatened species</t>
-  </si>
-  <si>
-    <t>15.6.1</t>
-  </si>
-  <si>
-    <t>Number of countries that have adopted legislative, administrative and policy frameworks to ensure fair and equitable sharing of benefits</t>
-  </si>
-  <si>
-    <t>15.6</t>
-  </si>
-  <si>
-    <t>Promote fair and equitable sharing of the benefits arising from the utilization of genetic resources and promote appropriate access to such resources, as internationally agreed</t>
-  </si>
-  <si>
-    <t>15.7.1</t>
-  </si>
-  <si>
-    <t>Proportion of traded wildlife that was poached or illicitly trafficked</t>
-  </si>
-  <si>
-    <t>15.7</t>
-  </si>
-  <si>
-    <t>Take urgent action to end poaching and trafficking of protected species of flora and fauna and address both demand and supply of illegal wildlife products</t>
-  </si>
-  <si>
-    <t>15.8.1</t>
-  </si>
-  <si>
-    <t>Proportion of countries adopting relevant national legislation and adequately resourcing the prevention or control of invasive alien species</t>
-  </si>
-  <si>
-    <t>15.8</t>
-  </si>
-  <si>
-    <t>By 2020, introduce measures to prevent the introduction and significantly reduce the impact of invasive alien species on land and water ecosystems and control or eradicate the priority species</t>
-  </si>
-  <si>
-    <t>15.9.1</t>
-  </si>
-  <si>
-    <t>(a) Number of countries that have established national targets in accordance with or similar to Aichi Biodiversity Target 2 of the Strategic Plan for Biodiversity 2011–2020 in their national biodiversity strategy and action plans and the progress reported towards these targets; and (b) integration of biodiversity into national accounting and reporting systems, defined as implementation of the System of Environmental-Economic Accounting</t>
-  </si>
-  <si>
-    <t>15.9</t>
-  </si>
-  <si>
-    <t>By 2020, integrate ecosystem and biodiversity values into national and local planning, development processes, poverty reduction strategies and accounts</t>
-  </si>
-  <si>
-    <t>15.a.1</t>
-  </si>
-  <si>
-    <t>(a) Official development assistance on conservation and sustainable use of biodiversity; and (b) revenue generated and finance mobilized from biodiversity-relevant economic instruments</t>
-  </si>
-  <si>
-    <t>15.a</t>
-  </si>
-  <si>
-    <t>Mobilize and significantly increase financial resources from all sources to conserve and sustainably use biodiversity and ecosystems</t>
-  </si>
-  <si>
-    <t>15.b.1</t>
-  </si>
-  <si>
-    <t>15.b</t>
-  </si>
-  <si>
-    <t>Mobilize significant resources from all sources and at all levels to finance sustainable forest management and provide adequate incentives to developing countries to advance such management, including for conservation and reforestation</t>
-  </si>
-  <si>
-    <t>15.c.1</t>
-  </si>
-  <si>
-    <t>15.c</t>
-  </si>
-  <si>
-    <t>Enhance global support for efforts to combat poaching and trafficking of protected species, including by increasing the capacity of local communities to pursue sustainable livelihood opportunities</t>
-  </si>
-  <si>
-    <t>16.1.1</t>
-  </si>
-  <si>
-    <t>Number of victims of intentional homicide per 100,000 population, by sex and age</t>
-  </si>
-  <si>
-    <t>16.1</t>
-  </si>
-  <si>
-    <t>Significantly reduce all forms of violence and related death rates everywhere</t>
-  </si>
-  <si>
-    <t>16.1.2</t>
-  </si>
-  <si>
-    <t>Conflict-related deaths per 100,000 population, by sex, age and cause</t>
-  </si>
-  <si>
-    <t>16.1.3</t>
-  </si>
-  <si>
-    <t>Proportion of population subjected to (a) physical violence, (b) psychological violence and (c) sexual violence in the previous 12 months</t>
-  </si>
-  <si>
-    <t>16.1.4</t>
-  </si>
-  <si>
-    <t>Proportion of population that feel safe walking alone around the area they live</t>
-  </si>
-  <si>
-    <t>16.2.1</t>
-  </si>
-  <si>
-    <t>Proportion of children aged 1-17 years who experienced any physical punishment and/or psychological aggression by caregivers in the past month</t>
-  </si>
-  <si>
-    <t>16.2</t>
-  </si>
-  <si>
-    <t>End abuse, exploitation, trafficking and all forms of violence against and torture of children</t>
-  </si>
-  <si>
-    <t>16.2.2</t>
-  </si>
-  <si>
-    <t>Number of victims of human trafficking per 100,000 population, by sex, age and form of exploitation</t>
-  </si>
-  <si>
-    <t>16.2.3</t>
-  </si>
-  <si>
-    <t>Proportion of young women and men aged 18-29 years who experienced sexual violence by age 18</t>
-  </si>
-  <si>
-    <t>16.3.1</t>
-  </si>
-  <si>
-    <t>Proportion of victims of violence in the previous 12 months who reported their victimization to competent authorities or other officially recognized conflict resolution mechanisms</t>
-  </si>
-  <si>
-    <t>16.3</t>
-  </si>
-  <si>
-    <t>Promote the rule of law at the national and international levels and ensure equal access to justice for all</t>
-  </si>
-  <si>
-    <t>16.3.2</t>
-  </si>
-  <si>
-    <t>Unsentenced detainees as a proportion of overall prison population</t>
-  </si>
-  <si>
-    <t>16.3.3</t>
-  </si>
-  <si>
-    <t>Proportion of the population who have experienced a dispute in the past two years and who accessed a formal or informal dispute resolution mechanism, by type of mechanism</t>
-  </si>
-  <si>
-    <t>16.4.1</t>
-  </si>
-  <si>
-    <t>Total value of inward and outward illicit financial flows (in current United States dollars)</t>
-  </si>
-  <si>
-    <t>16.4</t>
-  </si>
-  <si>
-    <t>By 2030, significantly reduce illicit financial and arms flows, strengthen the recovery and return of stolen assets and combat all forms of organized crime</t>
-  </si>
-  <si>
-    <t>16.4.2</t>
-  </si>
-  <si>
-    <t>Proportion of seized, found or surrendered arms whose illicit origin or context has been traced or established by a competent authority in line with international instruments</t>
-  </si>
-  <si>
-    <t>16.5.1</t>
-  </si>
-  <si>
-    <t>Proportion of persons who had at least one contact with a public official and who paid a bribe to a public official, or were asked for a bribe by those public officials, during the previous 12 months</t>
-  </si>
-  <si>
-    <t>16.5</t>
-  </si>
-  <si>
-    <t>Substantially reduce corruption and bribery in all their forms</t>
-  </si>
-  <si>
-    <t>16.5.2</t>
-  </si>
-  <si>
-    <t>Proportion of businesses that had at least one contact with a public official and that paid a bribe to a public official, or were asked for a bribe by those public officials during the previous 12 months</t>
-  </si>
-  <si>
-    <t>16.6.1</t>
-  </si>
-  <si>
-    <t>Primary government expenditures as a proportion of original approved budget, by sector (or by budget codes or similar)</t>
-  </si>
-  <si>
-    <t>16.6</t>
-  </si>
-  <si>
-    <t>Develop effective, accountable and transparent institutions at all levels</t>
-  </si>
-  <si>
-    <t>16.6.2</t>
-  </si>
-  <si>
-    <t>Proportion of population satisfied with their last experience of public services</t>
-  </si>
-  <si>
-    <t>16.7.1</t>
-  </si>
-  <si>
-    <t>Proportions of positions in national and local institutions, including (a) the legislatures; (b) the public service; and (c) the judiciary, compared to national distributions, by sex, age, persons with disabilities and population groups</t>
-  </si>
-  <si>
-    <t>16.7</t>
-  </si>
-  <si>
-    <t>Ensure responsive, inclusive, participatory and representative decision-making at all levels</t>
-  </si>
-  <si>
-    <t>16.7.2</t>
-  </si>
-  <si>
-    <t>Proportion of population who believe decision-making is inclusive and responsive, by sex, age, disability and population group</t>
-  </si>
-  <si>
-    <t>16.8.1</t>
-  </si>
-  <si>
-    <t>16.8</t>
-  </si>
-  <si>
-    <t>Broaden and strengthen the participation of developing countries in the institutions of global governance</t>
-  </si>
-  <si>
-    <t>16.9.1</t>
-  </si>
-  <si>
-    <t>Proportion of children under 5 years of age whose births have been registered with a civil authority, by age</t>
-  </si>
-  <si>
-    <t>16.9</t>
-  </si>
-  <si>
-    <t>By 2030, provide legal identity for all, including birth registration</t>
-  </si>
-  <si>
-    <t>16.10.1</t>
-  </si>
-  <si>
-    <t>Number of verified cases of killing, kidnapping, enforced disappearance, arbitrary detention and torture of journalists, associated media personnel, trade unionists and human rights advocates in the previous 12 months</t>
-  </si>
-  <si>
-    <t>16.10</t>
-  </si>
-  <si>
-    <t>Ensure public access to information and protect fundamental freedoms, in accordance with national legislation and international agreements</t>
-  </si>
-  <si>
-    <t>16.10.2</t>
-  </si>
-  <si>
-    <t>Number of countries that adopt and implement constitutional, statutory and/or policy guarantees for public access to information</t>
-  </si>
-  <si>
-    <t>16.a.1</t>
-  </si>
-  <si>
-    <t>Existence of independent national human rights institutions in compliance with the Paris Principles</t>
-  </si>
-  <si>
-    <t>16.a</t>
-  </si>
-  <si>
-    <t>Strengthen relevant national institutions, including through international cooperation, for building capacity at all levels, in particular in developing countries, to prevent violence and combat terrorism and crime</t>
-  </si>
-  <si>
-    <t>16.b.1</t>
-  </si>
-  <si>
     <t>16.b</t>
   </si>
   <si>
@@ -2302,7 +2305,7 @@
     <t>17.6.1</t>
   </si>
   <si>
-    <t>Fixed Internet broadband subscriptions per 100 inhabitants, by speed</t>
+    <t>Fixed Internet broadband subscriptions per 100 inhabitants, by speed</t>
   </si>
   <si>
     <t>17.6</t>
@@ -2338,7 +2341,7 @@
     <t>17.9.1</t>
   </si>
   <si>
-    <t>Dollar value of financial and technical assistance (including through North-South, South-South and triangular cooperation) committed to developing countries</t>
+    <t>Dollar value of financial and technical assistance (including through North-South, South‑South and triangular cooperation) committed to developing countries</t>
   </si>
   <si>
     <t>17.9</t>
@@ -2482,7 +2485,7 @@
     <t>17.19.2</t>
   </si>
   <si>
-    <t>Proportion of countries that (a) have conducted at least one population and housing census in the last 10 years; and (b) have achieved 100 per cent birth registration and 80 per cent death registration</t>
+    <t>Proportion of countries that (a) have conducted at least one population and housing census in the last 10 years; and (b) have achieved 100 per cent birth registration and 80 per cent death registration</t>
   </si>
 </sst>
 </file>
@@ -6619,424 +6622,424 @@
         <v>734</v>
       </c>
       <c r="B224" t="s">
-        <v>429</v>
+        <v>735</v>
       </c>
       <c r="D224" t="s">
         <v>9</v>
       </c>
       <c r="E224" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F224" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="225" spans="1:6">
       <c r="A225" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B225" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D225" t="s">
         <v>9</v>
       </c>
       <c r="E225" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F225" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="226" spans="1:6">
       <c r="A226" t="s">
+        <v>742</v>
+      </c>
+      <c r="B226" t="s">
+        <v>743</v>
+      </c>
+      <c r="D226" t="s">
+        <v>9</v>
+      </c>
+      <c r="E226" t="s">
+        <v>740</v>
+      </c>
+      <c r="F226" t="s">
         <v>741</v>
-      </c>
-      <c r="B226" t="s">
-        <v>742</v>
-      </c>
-      <c r="D226" t="s">
-        <v>9</v>
-      </c>
-      <c r="E226" t="s">
-        <v>739</v>
-      </c>
-      <c r="F226" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="227" spans="1:6">
       <c r="A227" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B227" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D227" t="s">
         <v>9</v>
       </c>
       <c r="E227" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F227" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="228" spans="1:6">
       <c r="A228" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B228" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D228" t="s">
         <v>9</v>
       </c>
       <c r="E228" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F228" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
+        <v>752</v>
+      </c>
+      <c r="B229" t="s">
+        <v>753</v>
+      </c>
+      <c r="D229" t="s">
+        <v>9</v>
+      </c>
+      <c r="E229" t="s">
+        <v>750</v>
+      </c>
+      <c r="F229" t="s">
         <v>751</v>
-      </c>
-      <c r="B229" t="s">
-        <v>752</v>
-      </c>
-      <c r="D229" t="s">
-        <v>9</v>
-      </c>
-      <c r="E229" t="s">
-        <v>749</v>
-      </c>
-      <c r="F229" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="230" spans="1:6">
       <c r="A230" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B230" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D230" t="s">
         <v>9</v>
       </c>
       <c r="E230" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F230" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="231" spans="1:6">
       <c r="A231" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B231" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D231" t="s">
         <v>9</v>
       </c>
       <c r="E231" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F231" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="232" spans="1:6">
       <c r="A232" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B232" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D232" t="s">
         <v>9</v>
       </c>
       <c r="E232" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="F232" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="233" spans="1:6">
       <c r="A233" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B233" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D233" t="s">
         <v>9</v>
       </c>
       <c r="E233" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="F233" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="234" spans="1:6">
       <c r="A234" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B234" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D234" t="s">
         <v>9</v>
       </c>
       <c r="E234" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="F234" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="235" spans="1:6">
       <c r="A235" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B235" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D235" t="s">
         <v>9</v>
       </c>
       <c r="E235" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="F235" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="236" spans="1:6">
       <c r="A236" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B236" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D236" t="s">
         <v>9</v>
       </c>
       <c r="E236" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="F236" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="237" spans="1:6">
       <c r="A237" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B237" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D237" t="s">
         <v>9</v>
       </c>
       <c r="E237" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F237" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="238" spans="1:6">
       <c r="A238" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B238" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D238" t="s">
         <v>9</v>
       </c>
       <c r="E238" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="F238" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="239" spans="1:6">
       <c r="A239" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B239" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D239" t="s">
         <v>9</v>
       </c>
       <c r="E239" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="F239" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B240" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D240" t="s">
         <v>9</v>
       </c>
       <c r="E240" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="F240" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="241" spans="1:6">
       <c r="A241" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B241" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D241" t="s">
         <v>9</v>
       </c>
       <c r="E241" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="F241" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="242" spans="1:6">
       <c r="A242" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B242" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D242" t="s">
         <v>9</v>
       </c>
       <c r="E242" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="F242" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="243" spans="1:6">
       <c r="A243" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B243" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D243" t="s">
         <v>9</v>
       </c>
       <c r="E243" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="F243" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="244" spans="1:6">
       <c r="A244" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B244" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D244" t="s">
         <v>9</v>
       </c>
       <c r="E244" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="F244" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="245" spans="1:6">
       <c r="A245" t="s">
+        <v>814</v>
+      </c>
+      <c r="B245" t="s">
+        <v>815</v>
+      </c>
+      <c r="D245" t="s">
+        <v>9</v>
+      </c>
+      <c r="E245" t="s">
+        <v>812</v>
+      </c>
+      <c r="F245" t="s">
         <v>813</v>
-      </c>
-      <c r="B245" t="s">
-        <v>814</v>
-      </c>
-      <c r="D245" t="s">
-        <v>9</v>
-      </c>
-      <c r="E245" t="s">
-        <v>811</v>
-      </c>
-      <c r="F245" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="246" spans="1:6">
       <c r="A246" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B246" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D246" t="s">
         <v>9</v>
       </c>
       <c r="E246" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="F246" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="247" spans="1:6">
       <c r="A247" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B247" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D247" t="s">
         <v>9</v>
       </c>
       <c r="E247" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="F247" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="248" spans="1:6">
       <c r="A248" t="s">
+        <v>822</v>
+      </c>
+      <c r="B248" t="s">
+        <v>823</v>
+      </c>
+      <c r="D248" t="s">
+        <v>9</v>
+      </c>
+      <c r="E248" t="s">
+        <v>820</v>
+      </c>
+      <c r="F248" t="s">
         <v>821</v>
-      </c>
-      <c r="B248" t="s">
-        <v>822</v>
-      </c>
-      <c r="D248" t="s">
-        <v>9</v>
-      </c>
-      <c r="E248" t="s">
-        <v>819</v>
-      </c>
-      <c r="F248" t="s">
-        <v>820</v>
       </c>
     </row>
   </sheetData>
